--- a/Stock_OneClick/history/scan_result_20260604_132400.xlsx
+++ b/Stock_OneClick/history/scan_result_20260604_132400.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q287"/>
+  <dimension ref="A1:Q286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -672,24 +672,12 @@
       <c r="J3" s="4" t="n">
         <v>190.76</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-04; 相对D0=-5.99%; 本次触发=2026-06-04(预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-04</t>
@@ -741,24 +729,6 @@
       <c r="J4" t="n">
         <v>16.53</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-04; 相对D0=2.54%; 本次触发=2026-06-04(预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-04</t>
@@ -810,24 +780,6 @@
       <c r="J5" t="n">
         <v>51.58</v>
       </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>D0=50.66; 最新=2026-06-04; 相对D0=1.82%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复4次; 重复日期=2026-05-27, 2026-06-01, 2026-06-03, 2026-06-04</t>
@@ -879,24 +831,12 @@
       <c r="J6" s="4" t="n">
         <v>186.69</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-06-04; 相对D0=4.09%; 本次触发=2026-06-04(正式买入); 历史重复4次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01, 2026-06-04</t>
@@ -948,24 +888,12 @@
       <c r="J7" s="4" t="n">
         <v>14.14</v>
       </c>
-      <c r="K7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-04; 相对D0=8.60%; 本次触发=2026-06-04(预警买入); 历史重复4次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02, 2026-06-04</t>
@@ -1017,24 +945,6 @@
       <c r="J8" t="n">
         <v>396.47</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=388.47; 最新=2026-06-04; 相对D0=2.06%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-27, 2026-06-03, 2026-06-04</t>
@@ -1086,24 +996,12 @@
       <c r="J9" s="4" t="n">
         <v>372.19</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-04; 相对D0=-4.29%; 本次触发=2026-06-04(预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-04</t>
@@ -1155,24 +1053,6 @@
       <c r="J10" t="n">
         <v>17.15</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=15.98; 最新=2026-06-04; 相对D0=7.32%; 本次触发=2026-06-04(正式买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1224,24 +1104,6 @@
       <c r="J11" t="n">
         <v>88.33</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=76.23; 最新=2026-06-04; 相对D0=15.87%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-04</t>
@@ -1293,24 +1155,12 @@
       <c r="J12" s="4" t="n">
         <v>119.36</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-04; 相对D0=16.88%; 本次触发=2026-06-04(预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1362,24 +1212,6 @@
       <c r="J13" t="n">
         <v>291.37</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-04; 相对D0=0.47%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-06-02, 2026-06-04</t>
@@ -1431,24 +1263,6 @@
       <c r="J14" t="n">
         <v>90.7</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=83.68; 最新=2026-06-04; 相对D0=8.39%; 本次触发=2026-06-04(预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1500,24 +1314,6 @@
       <c r="J15" t="n">
         <v>66.5</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-04; 相对D0=-1.31%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-06-02, 2026-06-04</t>
@@ -1569,24 +1365,6 @@
       <c r="J16" t="n">
         <v>279.25</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-04; 相对D0=8.33%; 本次触发=2026-06-04(预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1638,24 +1416,12 @@
       <c r="J17" s="4" t="n">
         <v>258.42</v>
       </c>
-      <c r="K17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-04; 相对D0=-0.30%; 本次触发=2026-06-04(预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1707,24 +1473,12 @@
       <c r="J18" s="4" t="n">
         <v>218.66</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-04; 相对D0=3.56%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-04</t>
@@ -1776,24 +1530,6 @@
       <c r="J19" t="n">
         <v>52.21</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-04; 相对D0=1.22%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-06-02, 2026-06-04</t>
@@ -1845,27 +1581,9 @@
       <c r="J20" t="n">
         <v>322.24</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>D0=320.41; 最新=2026-06-04; 相对D0=0.57%; 本次触发=2026-06-04(正式买入 | 第一买入点 | 预警买入); 历史重复1次; 重复日期=2026-06-04</t>
+          <t>D0=320.41; 最新=2026-06-04; 相对D0=0.57%; 本次触发=2026-06-04(正式买入 | 第一观察点 | 预警买入); 历史重复1次; 重复日期=2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1914,24 +1632,12 @@
       <c r="J21" s="4" t="n">
         <v>945.08</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-04; 相对D0=4.43%; 本次触发=2026-06-04(预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1983,24 +1689,12 @@
       <c r="J22" s="4" t="n">
         <v>217.5</v>
       </c>
-      <c r="K22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>D0=229.00; 最新=2026-06-04; 相对D0=-5.02%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -2052,24 +1746,6 @@
       <c r="J23" t="n">
         <v>11.29</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>D0=11.72; 最新=2026-06-04; 相对D0=-3.67%; 本次触发=2026-06-04(预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -2121,24 +1797,6 @@
       <c r="J24" t="n">
         <v>117.52</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=116.60; 最新=2026-06-04; 相对D0=0.79%; 本次触发=2026-06-04(正式买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -2190,24 +1848,6 @@
       <c r="J25" t="n">
         <v>91.62</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=90.49; 最新=2026-06-04; 相对D0=1.25%; 本次触发=2026-06-04(预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -2259,24 +1899,12 @@
       <c r="J26" s="4" t="n">
         <v>258.42</v>
       </c>
-      <c r="K26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O26" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P26" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>D0=258.42; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2328,27 +1956,9 @@
       <c r="J27" t="n">
         <v>322.24</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>D0=322.24; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=322.24; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -2397,24 +2007,6 @@
       <c r="J28" t="n">
         <v>291.37</v>
       </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v/>
-      </c>
-      <c r="M28" t="n">
-        <v/>
-      </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
-      <c r="O28" t="n">
-        <v/>
-      </c>
-      <c r="P28" t="n">
-        <v/>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>D0=291.37; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2466,24 +2058,12 @@
       <c r="J29" s="4" t="n">
         <v>190.76</v>
       </c>
-      <c r="K29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>D0=190.76; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2535,24 +2115,6 @@
       <c r="J30" t="n">
         <v>117.52</v>
       </c>
-      <c r="K30" t="n">
-        <v/>
-      </c>
-      <c r="L30" t="n">
-        <v/>
-      </c>
-      <c r="M30" t="n">
-        <v/>
-      </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
-      <c r="O30" t="n">
-        <v/>
-      </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>D0=117.52; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入)</t>
@@ -2604,24 +2166,6 @@
       <c r="J31" t="n">
         <v>90.7</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=90.70; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2673,24 +2217,6 @@
       <c r="J32" t="n">
         <v>16.53</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=16.53; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2742,24 +2268,12 @@
       <c r="J33" s="4" t="n">
         <v>217.5</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=217.50; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2811,24 +2325,6 @@
       <c r="J34" t="n">
         <v>66.5</v>
       </c>
-      <c r="K34" t="n">
-        <v/>
-      </c>
-      <c r="L34" t="n">
-        <v/>
-      </c>
-      <c r="M34" t="n">
-        <v/>
-      </c>
-      <c r="N34" t="n">
-        <v/>
-      </c>
-      <c r="O34" t="n">
-        <v/>
-      </c>
-      <c r="P34" t="n">
-        <v/>
-      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>D0=66.50; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2880,24 +2376,12 @@
       <c r="J35" s="4" t="n">
         <v>372.19</v>
       </c>
-      <c r="K35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>D0=372.19; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2949,24 +2433,6 @@
       <c r="J36" t="n">
         <v>82.65000000000001</v>
       </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>D0=82.65; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3018,24 +2484,6 @@
       <c r="J37" t="n">
         <v>88.33</v>
       </c>
-      <c r="K37" t="n">
-        <v/>
-      </c>
-      <c r="L37" t="n">
-        <v/>
-      </c>
-      <c r="M37" t="n">
-        <v/>
-      </c>
-      <c r="N37" t="n">
-        <v/>
-      </c>
-      <c r="O37" t="n">
-        <v/>
-      </c>
-      <c r="P37" t="n">
-        <v/>
-      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>D0=88.33; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -3087,24 +2535,6 @@
       <c r="J38" t="n">
         <v>301.77</v>
       </c>
-      <c r="K38" t="n">
-        <v/>
-      </c>
-      <c r="L38" t="n">
-        <v/>
-      </c>
-      <c r="M38" t="n">
-        <v/>
-      </c>
-      <c r="N38" t="n">
-        <v/>
-      </c>
-      <c r="O38" t="n">
-        <v/>
-      </c>
-      <c r="P38" t="n">
-        <v/>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>D0=301.77; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3156,24 +2586,6 @@
       <c r="J39" t="n">
         <v>51.58</v>
       </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -3225,24 +2637,6 @@
       <c r="J40" t="n">
         <v>52.07</v>
       </c>
-      <c r="K40" t="n">
-        <v/>
-      </c>
-      <c r="L40" t="n">
-        <v/>
-      </c>
-      <c r="M40" t="n">
-        <v/>
-      </c>
-      <c r="N40" t="n">
-        <v/>
-      </c>
-      <c r="O40" t="n">
-        <v/>
-      </c>
-      <c r="P40" t="n">
-        <v/>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>D0=52.07; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3294,24 +2688,12 @@
       <c r="J41" s="4" t="n">
         <v>186.69</v>
       </c>
-      <c r="K41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
+      <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>D0=186.69; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入)</t>
@@ -3363,24 +2745,12 @@
       <c r="J42" s="4" t="n">
         <v>945.08</v>
       </c>
-      <c r="K42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>D0=945.08; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3432,24 +2802,6 @@
       <c r="J43" t="n">
         <v>11.29</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=11.29; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3501,24 +2853,12 @@
       <c r="J44" s="4" t="n">
         <v>119.36</v>
       </c>
-      <c r="K44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n"/>
+      <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>D0=119.36; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3570,24 +2910,12 @@
       <c r="J45" s="4" t="n">
         <v>218.66</v>
       </c>
-      <c r="K45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
+      <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>D0=218.66; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -3639,24 +2967,6 @@
       <c r="J46" t="n">
         <v>279.25</v>
       </c>
-      <c r="K46" t="n">
-        <v/>
-      </c>
-      <c r="L46" t="n">
-        <v/>
-      </c>
-      <c r="M46" t="n">
-        <v/>
-      </c>
-      <c r="N46" t="n">
-        <v/>
-      </c>
-      <c r="O46" t="n">
-        <v/>
-      </c>
-      <c r="P46" t="n">
-        <v/>
-      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>D0=279.25; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3708,24 +3018,12 @@
       <c r="J47" s="4" t="n">
         <v>244.18</v>
       </c>
-      <c r="K47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>D0=244.18; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3777,24 +3075,6 @@
       <c r="J48" t="n">
         <v>91.62</v>
       </c>
-      <c r="K48" t="n">
-        <v/>
-      </c>
-      <c r="L48" t="n">
-        <v/>
-      </c>
-      <c r="M48" t="n">
-        <v/>
-      </c>
-      <c r="N48" t="n">
-        <v/>
-      </c>
-      <c r="O48" t="n">
-        <v/>
-      </c>
-      <c r="P48" t="n">
-        <v/>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>D0=91.62; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3846,24 +3126,6 @@
       <c r="J49" t="n">
         <v>17.15</v>
       </c>
-      <c r="K49" t="n">
-        <v/>
-      </c>
-      <c r="L49" t="n">
-        <v/>
-      </c>
-      <c r="M49" t="n">
-        <v/>
-      </c>
-      <c r="N49" t="n">
-        <v/>
-      </c>
-      <c r="O49" t="n">
-        <v/>
-      </c>
-      <c r="P49" t="n">
-        <v/>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>D0=17.15; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入)</t>
@@ -3915,24 +3177,12 @@
       <c r="J50" s="4" t="n">
         <v>14.14</v>
       </c>
-      <c r="K50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>D0=14.14; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3984,24 +3234,6 @@
       <c r="J51" t="n">
         <v>396.47</v>
       </c>
-      <c r="K51" t="n">
-        <v/>
-      </c>
-      <c r="L51" t="n">
-        <v/>
-      </c>
-      <c r="M51" t="n">
-        <v/>
-      </c>
-      <c r="N51" t="n">
-        <v/>
-      </c>
-      <c r="O51" t="n">
-        <v/>
-      </c>
-      <c r="P51" t="n">
-        <v/>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>D0=396.47; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -4053,24 +3285,6 @@
       <c r="J52" t="n">
         <v>52.21</v>
       </c>
-      <c r="K52" t="n">
-        <v/>
-      </c>
-      <c r="L52" t="n">
-        <v/>
-      </c>
-      <c r="M52" t="n">
-        <v/>
-      </c>
-      <c r="N52" t="n">
-        <v/>
-      </c>
-      <c r="O52" t="n">
-        <v/>
-      </c>
-      <c r="P52" t="n">
-        <v/>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>D0=52.21; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -4122,24 +3336,12 @@
       <c r="J53" s="4" t="n">
         <v>202.89</v>
       </c>
-      <c r="K53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
+      <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-04; 相对D0=11.79%; 历史重复3次; 重复日期=2026-05-27, 2026-06-01, 2026-06-03</t>
@@ -4191,24 +3393,12 @@
       <c r="J54" s="4" t="n">
         <v>181.16</v>
       </c>
-      <c r="K54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
+      <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-04; 相对D0=8.24%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -4260,24 +3450,12 @@
       <c r="J55" s="4" t="n">
         <v>264.59</v>
       </c>
-      <c r="K55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="inlineStr">
         <is>
           <t>D0=294.07; 最新=2026-06-04; 相对D0=-10.02%; 历史重复1次; 重复日期=2026-05-29</t>
@@ -4329,24 +3507,12 @@
       <c r="J56" s="4" t="n">
         <v>55.88</v>
       </c>
-      <c r="K56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O56" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P56" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-04; 相对D0=20.09%</t>
@@ -4398,24 +3564,12 @@
       <c r="J57" s="4" t="n">
         <v>188.75</v>
       </c>
-      <c r="K57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n"/>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n"/>
+      <c r="P57" s="4" t="n"/>
       <c r="Q57" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-04; 相对D0=4.82%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -4467,24 +3621,12 @@
       <c r="J58" s="4" t="n">
         <v>47.65</v>
       </c>
-      <c r="K58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P58" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
+      <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-04; 相对D0=-0.98%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -4536,24 +3678,12 @@
       <c r="J59" s="4" t="n">
         <v>139.88</v>
       </c>
-      <c r="K59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="n"/>
+      <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="inlineStr">
         <is>
           <t>D0=135.28; 最新=2026-06-04; 相对D0=3.40%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -4605,24 +3735,6 @@
       <c r="J60" t="n">
         <v>140.88</v>
       </c>
-      <c r="K60" t="n">
-        <v/>
-      </c>
-      <c r="L60" t="n">
-        <v/>
-      </c>
-      <c r="M60" t="n">
-        <v/>
-      </c>
-      <c r="N60" t="n">
-        <v/>
-      </c>
-      <c r="O60" t="n">
-        <v/>
-      </c>
-      <c r="P60" t="n">
-        <v/>
-      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-04; 相对D0=-0.24%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -4674,24 +3786,6 @@
       <c r="J61" t="n">
         <v>418.61</v>
       </c>
-      <c r="K61" t="n">
-        <v/>
-      </c>
-      <c r="L61" t="n">
-        <v/>
-      </c>
-      <c r="M61" t="n">
-        <v/>
-      </c>
-      <c r="N61" t="n">
-        <v/>
-      </c>
-      <c r="O61" t="n">
-        <v/>
-      </c>
-      <c r="P61" t="n">
-        <v/>
-      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-04; 相对D0=6.97%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -4743,24 +3837,6 @@
       <c r="J62" t="n">
         <v>963.33</v>
       </c>
-      <c r="K62" t="n">
-        <v/>
-      </c>
-      <c r="L62" t="n">
-        <v/>
-      </c>
-      <c r="M62" t="n">
-        <v/>
-      </c>
-      <c r="N62" t="n">
-        <v/>
-      </c>
-      <c r="O62" t="n">
-        <v/>
-      </c>
-      <c r="P62" t="n">
-        <v/>
-      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-04; 相对D0=-7.26%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -4812,24 +3888,12 @@
       <c r="J63" s="4" t="n">
         <v>380.18</v>
       </c>
-      <c r="K63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P63" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="4" t="n"/>
+      <c r="N63" s="4" t="n"/>
+      <c r="O63" s="4" t="n"/>
+      <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-04; 相对D0=16.57%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -4881,24 +3945,12 @@
       <c r="J64" s="4" t="n">
         <v>627.5700000000001</v>
       </c>
-      <c r="K64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P64" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="n"/>
+      <c r="O64" s="4" t="n"/>
+      <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="inlineStr">
         <is>
           <t>D0=610.26; 最新=2026-06-04; 相对D0=2.84%; 历史重复2次; 重复日期=2026-05-26, 2026-06-03</t>
@@ -4950,24 +4002,6 @@
       <c r="J65" t="n">
         <v>22.9</v>
       </c>
-      <c r="K65" t="n">
-        <v/>
-      </c>
-      <c r="L65" t="n">
-        <v/>
-      </c>
-      <c r="M65" t="n">
-        <v/>
-      </c>
-      <c r="N65" t="n">
-        <v/>
-      </c>
-      <c r="O65" t="n">
-        <v/>
-      </c>
-      <c r="P65" t="n">
-        <v/>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-04; 相对D0=1.73%; 历史重复3次; 重复日期=2026-05-26, 2026-06-02, 2026-06-03</t>
@@ -5019,24 +4053,12 @@
       <c r="J66" s="4" t="n">
         <v>26.16</v>
       </c>
-      <c r="K66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O66" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P66" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n"/>
+      <c r="P66" s="4" t="n"/>
       <c r="Q66" s="4" t="inlineStr">
         <is>
           <t>D0=26.73; 最新=2026-06-04; 相对D0=-2.13%</t>
@@ -5088,24 +4110,6 @@
       <c r="J67" t="n">
         <v>133.39</v>
       </c>
-      <c r="K67" t="n">
-        <v/>
-      </c>
-      <c r="L67" t="n">
-        <v/>
-      </c>
-      <c r="M67" t="n">
-        <v/>
-      </c>
-      <c r="N67" t="n">
-        <v/>
-      </c>
-      <c r="O67" t="n">
-        <v/>
-      </c>
-      <c r="P67" t="n">
-        <v/>
-      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>D0=137.65; 最新=2026-06-04; 相对D0=-3.09%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -5157,24 +4161,6 @@
       <c r="J68" t="n">
         <v>262.28</v>
       </c>
-      <c r="K68" t="n">
-        <v/>
-      </c>
-      <c r="L68" t="n">
-        <v/>
-      </c>
-      <c r="M68" t="n">
-        <v/>
-      </c>
-      <c r="N68" t="n">
-        <v/>
-      </c>
-      <c r="O68" t="n">
-        <v/>
-      </c>
-      <c r="P68" t="n">
-        <v/>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-04; 相对D0=13.05%</t>
@@ -5226,24 +4212,6 @@
       <c r="J69" t="n">
         <v>150.32</v>
       </c>
-      <c r="K69" t="n">
-        <v/>
-      </c>
-      <c r="L69" t="n">
-        <v/>
-      </c>
-      <c r="M69" t="n">
-        <v/>
-      </c>
-      <c r="N69" t="n">
-        <v/>
-      </c>
-      <c r="O69" t="n">
-        <v/>
-      </c>
-      <c r="P69" t="n">
-        <v/>
-      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-04; 相对D0=15.19%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -5295,24 +4263,12 @@
       <c r="J70" s="4" t="n">
         <v>274.76</v>
       </c>
-      <c r="K70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-04; 相对D0=4.77%; 历史重复3次; 重复日期=2026-05-26, 2026-05-27, 2026-06-02</t>
@@ -5364,24 +4320,6 @@
       <c r="J71" t="n">
         <v>58.67</v>
       </c>
-      <c r="K71" t="n">
-        <v/>
-      </c>
-      <c r="L71" t="n">
-        <v/>
-      </c>
-      <c r="M71" t="n">
-        <v/>
-      </c>
-      <c r="N71" t="n">
-        <v/>
-      </c>
-      <c r="O71" t="n">
-        <v/>
-      </c>
-      <c r="P71" t="n">
-        <v/>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>D0=58.81; 最新=2026-06-04; 相对D0=-0.24%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -5433,24 +4371,6 @@
       <c r="J72" t="n">
         <v>57.61</v>
       </c>
-      <c r="K72" t="n">
-        <v/>
-      </c>
-      <c r="L72" t="n">
-        <v/>
-      </c>
-      <c r="M72" t="n">
-        <v/>
-      </c>
-      <c r="N72" t="n">
-        <v/>
-      </c>
-      <c r="O72" t="n">
-        <v/>
-      </c>
-      <c r="P72" t="n">
-        <v/>
-      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>D0=54.94; 最新=2026-06-04; 相对D0=4.86%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -5502,24 +4422,6 @@
       <c r="J73" t="n">
         <v>84.13</v>
       </c>
-      <c r="K73" t="n">
-        <v/>
-      </c>
-      <c r="L73" t="n">
-        <v/>
-      </c>
-      <c r="M73" t="n">
-        <v/>
-      </c>
-      <c r="N73" t="n">
-        <v/>
-      </c>
-      <c r="O73" t="n">
-        <v/>
-      </c>
-      <c r="P73" t="n">
-        <v/>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>D0=81.76; 最新=2026-06-04; 相对D0=2.90%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -5571,24 +4473,12 @@
       <c r="J74" s="4" t="n">
         <v>101.5</v>
       </c>
-      <c r="K74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O74" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P74" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n"/>
+      <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-04; 相对D0=18.82%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -5640,24 +4530,12 @@
       <c r="J75" s="4" t="n">
         <v>418.45</v>
       </c>
-      <c r="K75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O75" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P75" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
+      <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-04; 相对D0=-1.77%</t>
@@ -5709,24 +4587,6 @@
       <c r="J76" t="n">
         <v>153.7</v>
       </c>
-      <c r="K76" t="n">
-        <v/>
-      </c>
-      <c r="L76" t="n">
-        <v/>
-      </c>
-      <c r="M76" t="n">
-        <v/>
-      </c>
-      <c r="N76" t="n">
-        <v/>
-      </c>
-      <c r="O76" t="n">
-        <v/>
-      </c>
-      <c r="P76" t="n">
-        <v/>
-      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>D0=156.27; 最新=2026-06-04; 相对D0=-1.64%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -5778,24 +4638,6 @@
       <c r="J77" t="n">
         <v>51.62</v>
       </c>
-      <c r="K77" t="n">
-        <v/>
-      </c>
-      <c r="L77" t="n">
-        <v/>
-      </c>
-      <c r="M77" t="n">
-        <v/>
-      </c>
-      <c r="N77" t="n">
-        <v/>
-      </c>
-      <c r="O77" t="n">
-        <v/>
-      </c>
-      <c r="P77" t="n">
-        <v/>
-      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>D0=50.29; 最新=2026-06-04; 相对D0=2.64%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -5847,24 +4689,12 @@
       <c r="J78" s="4" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="K78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O78" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P78" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K78" s="4" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="4" t="n"/>
+      <c r="N78" s="4" t="n"/>
+      <c r="O78" s="4" t="n"/>
+      <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-04; 相对D0=0.49%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -5916,24 +4746,6 @@
       <c r="J79" t="n">
         <v>418.91</v>
       </c>
-      <c r="K79" t="n">
-        <v/>
-      </c>
-      <c r="L79" t="n">
-        <v/>
-      </c>
-      <c r="M79" t="n">
-        <v/>
-      </c>
-      <c r="N79" t="n">
-        <v/>
-      </c>
-      <c r="O79" t="n">
-        <v/>
-      </c>
-      <c r="P79" t="n">
-        <v/>
-      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-04; 相对D0=-0.73%</t>
@@ -5985,24 +4797,6 @@
       <c r="J80" t="n">
         <v>88.78</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-04; 相对D0=2.65%</t>
@@ -6054,24 +4848,12 @@
       <c r="J81" s="4" t="n">
         <v>190.76</v>
       </c>
-      <c r="K81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P81" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K81" s="4" t="n"/>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="4" t="n"/>
+      <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="n"/>
+      <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-04; 相对D0=-6.66%</t>
@@ -6123,24 +4905,12 @@
       <c r="J82" s="4" t="n">
         <v>181.16</v>
       </c>
-      <c r="K82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P82" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
+      <c r="O82" s="4" t="n"/>
+      <c r="P82" s="4" t="n"/>
       <c r="Q82" s="4" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-04; 相对D0=3.68%</t>
@@ -6192,24 +4962,12 @@
       <c r="J83" s="4" t="n">
         <v>114.02</v>
       </c>
-      <c r="K83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="4" t="n"/>
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="4" t="n"/>
+      <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="n"/>
+      <c r="P83" s="4" t="n"/>
       <c r="Q83" s="4" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-04; 相对D0=5.41%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -6261,24 +5019,6 @@
       <c r="J84" t="n">
         <v>108.03</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-04; 相对D0=2.02%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -6330,24 +5070,12 @@
       <c r="J85" s="4" t="n">
         <v>47.65</v>
       </c>
-      <c r="K85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P85" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="4" t="n"/>
+      <c r="O85" s="4" t="n"/>
+      <c r="P85" s="4" t="n"/>
       <c r="Q85" s="4" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-04; 相对D0=-3.66%</t>
@@ -6399,24 +5127,6 @@
       <c r="J86" t="n">
         <v>418.61</v>
       </c>
-      <c r="K86" t="n">
-        <v/>
-      </c>
-      <c r="L86" t="n">
-        <v/>
-      </c>
-      <c r="M86" t="n">
-        <v/>
-      </c>
-      <c r="N86" t="n">
-        <v/>
-      </c>
-      <c r="O86" t="n">
-        <v/>
-      </c>
-      <c r="P86" t="n">
-        <v/>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-04; 相对D0=3.84%</t>
@@ -6468,24 +5178,6 @@
       <c r="J87" t="n">
         <v>963.33</v>
       </c>
-      <c r="K87" t="n">
-        <v/>
-      </c>
-      <c r="L87" t="n">
-        <v/>
-      </c>
-      <c r="M87" t="n">
-        <v/>
-      </c>
-      <c r="N87" t="n">
-        <v/>
-      </c>
-      <c r="O87" t="n">
-        <v/>
-      </c>
-      <c r="P87" t="n">
-        <v/>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-04; 相对D0=-10.01%</t>
@@ -6537,24 +5229,12 @@
       <c r="J88" s="4" t="n">
         <v>186.69</v>
       </c>
-      <c r="K88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="4" t="n"/>
+      <c r="L88" s="4" t="n"/>
+      <c r="M88" s="4" t="n"/>
+      <c r="N88" s="4" t="n"/>
+      <c r="O88" s="4" t="n"/>
+      <c r="P88" s="4" t="n"/>
       <c r="Q88" s="4" t="inlineStr">
         <is>
           <t>D0=183.36; 最新=2026-06-04; 相对D0=1.82%</t>
@@ -6606,24 +5286,12 @@
       <c r="J89" s="4" t="n">
         <v>69.12</v>
       </c>
-      <c r="K89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+      <c r="O89" s="4" t="n"/>
+      <c r="P89" s="4" t="n"/>
       <c r="Q89" s="4" t="inlineStr">
         <is>
           <t>D0=69.63; 最新=2026-06-04; 相对D0=-0.73%</t>
@@ -6675,24 +5343,12 @@
       <c r="J90" s="4" t="n">
         <v>627.5700000000001</v>
       </c>
-      <c r="K90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P90" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K90" s="4" t="n"/>
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
+      <c r="N90" s="4" t="n"/>
+      <c r="O90" s="4" t="n"/>
+      <c r="P90" s="4" t="n"/>
       <c r="Q90" s="4" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-04; 相对D0=2.49%</t>
@@ -6744,24 +5400,6 @@
       <c r="J91" t="n">
         <v>22.9</v>
       </c>
-      <c r="K91" t="n">
-        <v/>
-      </c>
-      <c r="L91" t="n">
-        <v/>
-      </c>
-      <c r="M91" t="n">
-        <v/>
-      </c>
-      <c r="N91" t="n">
-        <v/>
-      </c>
-      <c r="O91" t="n">
-        <v/>
-      </c>
-      <c r="P91" t="n">
-        <v/>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>D0=22.62; 最新=2026-06-04; 相对D0=1.24%</t>
@@ -6813,24 +5451,12 @@
       <c r="J92" s="4" t="n">
         <v>131.57</v>
       </c>
-      <c r="K92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P92" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K92" s="4" t="n"/>
+      <c r="L92" s="4" t="n"/>
+      <c r="M92" s="4" t="n"/>
+      <c r="N92" s="4" t="n"/>
+      <c r="O92" s="4" t="n"/>
+      <c r="P92" s="4" t="n"/>
       <c r="Q92" s="4" t="inlineStr">
         <is>
           <t>D0=134.61; 最新=2026-06-04; 相对D0=-2.26%; 历史重复2次; 重复日期=2026-05-28, 2026-06-02</t>
@@ -6882,24 +5508,12 @@
       <c r="J93" s="4" t="n">
         <v>65.39</v>
       </c>
-      <c r="K93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P93" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K93" s="4" t="n"/>
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="4" t="n"/>
+      <c r="N93" s="4" t="n"/>
+      <c r="O93" s="4" t="n"/>
+      <c r="P93" s="4" t="n"/>
       <c r="Q93" s="4" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-04; 相对D0=-4.82%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -6951,24 +5565,12 @@
       <c r="J94" s="4" t="n">
         <v>274.76</v>
       </c>
-      <c r="K94" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L94" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M94" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N94" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O94" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P94" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="4" t="n"/>
+      <c r="O94" s="4" t="n"/>
+      <c r="P94" s="4" t="n"/>
       <c r="Q94" s="4" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-04; 相对D0=0.22%</t>
@@ -7020,24 +5622,6 @@
       <c r="J95" t="n">
         <v>57.61</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=56.31; 最新=2026-06-04; 相对D0=2.31%</t>
@@ -7089,24 +5673,6 @@
       <c r="J96" t="n">
         <v>105.4</v>
       </c>
-      <c r="K96" t="n">
-        <v/>
-      </c>
-      <c r="L96" t="n">
-        <v/>
-      </c>
-      <c r="M96" t="n">
-        <v/>
-      </c>
-      <c r="N96" t="n">
-        <v/>
-      </c>
-      <c r="O96" t="n">
-        <v/>
-      </c>
-      <c r="P96" t="n">
-        <v/>
-      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-04; 相对D0=-1.44%</t>
@@ -7158,24 +5724,12 @@
       <c r="J97" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="K97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P97" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K97" s="4" t="n"/>
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="4" t="n"/>
+      <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="n"/>
+      <c r="P97" s="4" t="n"/>
       <c r="Q97" s="4" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-04; 相对D0=-1.80%</t>
@@ -7227,24 +5781,6 @@
       <c r="J98" t="n">
         <v>84.13</v>
       </c>
-      <c r="K98" t="n">
-        <v/>
-      </c>
-      <c r="L98" t="n">
-        <v/>
-      </c>
-      <c r="M98" t="n">
-        <v/>
-      </c>
-      <c r="N98" t="n">
-        <v/>
-      </c>
-      <c r="O98" t="n">
-        <v/>
-      </c>
-      <c r="P98" t="n">
-        <v/>
-      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-04; 相对D0=-0.60%</t>
@@ -7296,24 +5832,12 @@
       <c r="J99" s="4" t="n">
         <v>14.14</v>
       </c>
-      <c r="K99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P99" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K99" s="4" t="n"/>
+      <c r="L99" s="4" t="n"/>
+      <c r="M99" s="4" t="n"/>
+      <c r="N99" s="4" t="n"/>
+      <c r="O99" s="4" t="n"/>
+      <c r="P99" s="4" t="n"/>
       <c r="Q99" s="4" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-04; 相对D0=4.66%</t>
@@ -7365,24 +5889,12 @@
       <c r="J100" s="4" t="n">
         <v>17.37</v>
       </c>
-      <c r="K100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P100" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K100" s="4" t="n"/>
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="4" t="n"/>
+      <c r="N100" s="4" t="n"/>
+      <c r="O100" s="4" t="n"/>
+      <c r="P100" s="4" t="n"/>
       <c r="Q100" s="4" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-04; 相对D0=-5.60%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -7434,24 +5946,6 @@
       <c r="J101" t="n">
         <v>323.92</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-04; 相对D0=0.00%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -7503,24 +5997,6 @@
       <c r="J102" t="n">
         <v>51.62</v>
       </c>
-      <c r="K102" t="n">
-        <v/>
-      </c>
-      <c r="L102" t="n">
-        <v/>
-      </c>
-      <c r="M102" t="n">
-        <v/>
-      </c>
-      <c r="N102" t="n">
-        <v/>
-      </c>
-      <c r="O102" t="n">
-        <v/>
-      </c>
-      <c r="P102" t="n">
-        <v/>
-      </c>
       <c r="Q102" t="inlineStr">
         <is>
           <t>D0=50.99; 最新=2026-06-04; 相对D0=1.24%</t>
@@ -7572,24 +6048,12 @@
       <c r="J103" s="4" t="n">
         <v>202.89</v>
       </c>
-      <c r="K103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P103" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="4" t="n"/>
+      <c r="O103" s="4" t="n"/>
+      <c r="P103" s="4" t="n"/>
       <c r="Q103" s="4" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-04; 相对D0=12.82%</t>
@@ -7641,24 +6105,12 @@
       <c r="J104" s="4" t="n">
         <v>253.79</v>
       </c>
-      <c r="K104" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L104" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M104" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N104" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O104" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P104" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K104" s="4" t="n"/>
+      <c r="L104" s="4" t="n"/>
+      <c r="M104" s="4" t="n"/>
+      <c r="N104" s="4" t="n"/>
+      <c r="O104" s="4" t="n"/>
+      <c r="P104" s="4" t="n"/>
       <c r="Q104" s="4" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-04; 相对D0=-6.64%</t>
@@ -7679,7 +6131,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7706,24 +6157,6 @@
       <c r="J105" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="K105" t="n">
-        <v/>
-      </c>
-      <c r="L105" t="n">
-        <v/>
-      </c>
-      <c r="M105" t="n">
-        <v/>
-      </c>
-      <c r="N105" t="n">
-        <v/>
-      </c>
-      <c r="O105" t="n">
-        <v/>
-      </c>
-      <c r="P105" t="n">
-        <v/>
-      </c>
       <c r="Q105" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-04; 相对D0=3.21%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -7775,24 +6208,6 @@
       <c r="J106" t="n">
         <v>16.53</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-04; 相对D0=0.43%</t>
@@ -7844,24 +6259,6 @@
       <c r="J107" t="n">
         <v>28.01</v>
       </c>
-      <c r="K107" t="n">
-        <v/>
-      </c>
-      <c r="L107" t="n">
-        <v/>
-      </c>
-      <c r="M107" t="n">
-        <v/>
-      </c>
-      <c r="N107" t="n">
-        <v/>
-      </c>
-      <c r="O107" t="n">
-        <v/>
-      </c>
-      <c r="P107" t="n">
-        <v/>
-      </c>
       <c r="Q107" t="inlineStr">
         <is>
           <t>D0=25.20; 最新=2026-06-04; 相对D0=11.15%</t>
@@ -7913,24 +6310,6 @@
       <c r="J108" t="n">
         <v>51.58</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=50.44; 最新=2026-06-04; 相对D0=2.26%</t>
@@ -7982,24 +6361,12 @@
       <c r="J109" s="4" t="n">
         <v>274.76</v>
       </c>
-      <c r="K109" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L109" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M109" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N109" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O109" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P109" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K109" s="4" t="n"/>
+      <c r="L109" s="4" t="n"/>
+      <c r="M109" s="4" t="n"/>
+      <c r="N109" s="4" t="n"/>
+      <c r="O109" s="4" t="n"/>
+      <c r="P109" s="4" t="n"/>
       <c r="Q109" s="4" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-04; 相对D0=2.95%</t>
@@ -8051,24 +6418,6 @@
       <c r="J110" t="n">
         <v>236.34</v>
       </c>
-      <c r="K110" t="n">
-        <v/>
-      </c>
-      <c r="L110" t="n">
-        <v/>
-      </c>
-      <c r="M110" t="n">
-        <v/>
-      </c>
-      <c r="N110" t="n">
-        <v/>
-      </c>
-      <c r="O110" t="n">
-        <v/>
-      </c>
-      <c r="P110" t="n">
-        <v/>
-      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-04; 相对D0=23.76%</t>
@@ -8120,24 +6469,12 @@
       <c r="J111" s="4" t="n">
         <v>101.5</v>
       </c>
-      <c r="K111" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L111" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M111" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N111" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O111" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P111" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K111" s="4" t="n"/>
+      <c r="L111" s="4" t="n"/>
+      <c r="M111" s="4" t="n"/>
+      <c r="N111" s="4" t="n"/>
+      <c r="O111" s="4" t="n"/>
+      <c r="P111" s="4" t="n"/>
       <c r="Q111" s="4" t="inlineStr">
         <is>
           <t>D0=89.07; 最新=2026-06-04; 相对D0=13.96%</t>
@@ -8189,24 +6526,6 @@
       <c r="J112" t="n">
         <v>396.47</v>
       </c>
-      <c r="K112" t="n">
-        <v/>
-      </c>
-      <c r="L112" t="n">
-        <v/>
-      </c>
-      <c r="M112" t="n">
-        <v/>
-      </c>
-      <c r="N112" t="n">
-        <v/>
-      </c>
-      <c r="O112" t="n">
-        <v/>
-      </c>
-      <c r="P112" t="n">
-        <v/>
-      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>D0=384.01; 最新=2026-06-04; 相对D0=3.24%</t>
@@ -8227,7 +6546,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -8254,24 +6572,6 @@
       <c r="J113" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="K113" t="n">
-        <v/>
-      </c>
-      <c r="L113" t="n">
-        <v/>
-      </c>
-      <c r="M113" t="n">
-        <v/>
-      </c>
-      <c r="N113" t="n">
-        <v/>
-      </c>
-      <c r="O113" t="n">
-        <v/>
-      </c>
-      <c r="P113" t="n">
-        <v/>
-      </c>
       <c r="Q113" t="inlineStr">
         <is>
           <t>D0=91.09; 最新=2026-06-04; 相对D0=2.96%</t>
@@ -8323,24 +6623,12 @@
       <c r="J114" s="4" t="n">
         <v>114.02</v>
       </c>
-      <c r="K114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O114" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P114" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K114" s="4" t="n"/>
+      <c r="L114" s="4" t="n"/>
+      <c r="M114" s="4" t="n"/>
+      <c r="N114" s="4" t="n"/>
+      <c r="O114" s="4" t="n"/>
+      <c r="P114" s="4" t="n"/>
       <c r="Q114" s="4" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-04; 相对D0=3.06%</t>
@@ -8392,24 +6680,12 @@
       <c r="J115" s="4" t="n">
         <v>188.75</v>
       </c>
-      <c r="K115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O115" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P115" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K115" s="4" t="n"/>
+      <c r="L115" s="4" t="n"/>
+      <c r="M115" s="4" t="n"/>
+      <c r="N115" s="4" t="n"/>
+      <c r="O115" s="4" t="n"/>
+      <c r="P115" s="4" t="n"/>
       <c r="Q115" s="4" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-04; 相对D0=7.14%</t>
@@ -8461,24 +6737,6 @@
       <c r="J116" t="n">
         <v>719.09</v>
       </c>
-      <c r="K116" t="n">
-        <v/>
-      </c>
-      <c r="L116" t="n">
-        <v/>
-      </c>
-      <c r="M116" t="n">
-        <v/>
-      </c>
-      <c r="N116" t="n">
-        <v/>
-      </c>
-      <c r="O116" t="n">
-        <v/>
-      </c>
-      <c r="P116" t="n">
-        <v/>
-      </c>
       <c r="Q116" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-04; 相对D0=7.17%</t>
@@ -8530,24 +6788,6 @@
       <c r="J117" t="n">
         <v>108.03</v>
       </c>
-      <c r="K117" t="n">
-        <v/>
-      </c>
-      <c r="L117" t="n">
-        <v/>
-      </c>
-      <c r="M117" t="n">
-        <v/>
-      </c>
-      <c r="N117" t="n">
-        <v/>
-      </c>
-      <c r="O117" t="n">
-        <v/>
-      </c>
-      <c r="P117" t="n">
-        <v/>
-      </c>
       <c r="Q117" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-04; 相对D0=1.09%</t>
@@ -8568,7 +6808,6 @@
           <t>EQIX</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -8595,24 +6834,6 @@
       <c r="J118" t="n">
         <v>1089.15</v>
       </c>
-      <c r="K118" t="n">
-        <v/>
-      </c>
-      <c r="L118" t="n">
-        <v/>
-      </c>
-      <c r="M118" t="n">
-        <v/>
-      </c>
-      <c r="N118" t="n">
-        <v/>
-      </c>
-      <c r="O118" t="n">
-        <v/>
-      </c>
-      <c r="P118" t="n">
-        <v/>
-      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-04; 相对D0=1.84%</t>
@@ -8664,24 +6885,6 @@
       <c r="J119" t="n">
         <v>149.67</v>
       </c>
-      <c r="K119" t="n">
-        <v/>
-      </c>
-      <c r="L119" t="n">
-        <v/>
-      </c>
-      <c r="M119" t="n">
-        <v/>
-      </c>
-      <c r="N119" t="n">
-        <v/>
-      </c>
-      <c r="O119" t="n">
-        <v/>
-      </c>
-      <c r="P119" t="n">
-        <v/>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-04; 相对D0=15.40%</t>
@@ -8733,24 +6936,12 @@
       <c r="J120" s="4" t="n">
         <v>372.19</v>
       </c>
-      <c r="K120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O120" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P120" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K120" s="4" t="n"/>
+      <c r="L120" s="4" t="n"/>
+      <c r="M120" s="4" t="n"/>
+      <c r="N120" s="4" t="n"/>
+      <c r="O120" s="4" t="n"/>
+      <c r="P120" s="4" t="n"/>
       <c r="Q120" s="4" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-04; 相对D0=-4.60%</t>
@@ -8802,24 +6993,6 @@
       <c r="J121" t="n">
         <v>88.33</v>
       </c>
-      <c r="K121" t="n">
-        <v/>
-      </c>
-      <c r="L121" t="n">
-        <v/>
-      </c>
-      <c r="M121" t="n">
-        <v/>
-      </c>
-      <c r="N121" t="n">
-        <v/>
-      </c>
-      <c r="O121" t="n">
-        <v/>
-      </c>
-      <c r="P121" t="n">
-        <v/>
-      </c>
       <c r="Q121" t="inlineStr">
         <is>
           <t>D0=84.84; 最新=2026-06-04; 相对D0=4.11%</t>
@@ -8871,24 +7044,12 @@
       <c r="J122" s="4" t="n">
         <v>100.06</v>
       </c>
-      <c r="K122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O122" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P122" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K122" s="4" t="n"/>
+      <c r="L122" s="4" t="n"/>
+      <c r="M122" s="4" t="n"/>
+      <c r="N122" s="4" t="n"/>
+      <c r="O122" s="4" t="n"/>
+      <c r="P122" s="4" t="n"/>
       <c r="Q122" s="4" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-04; 相对D0=4.58%</t>
@@ -8940,24 +7101,12 @@
       <c r="J123" s="4" t="n">
         <v>186.69</v>
       </c>
-      <c r="K123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O123" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P123" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K123" s="4" t="n"/>
+      <c r="L123" s="4" t="n"/>
+      <c r="M123" s="4" t="n"/>
+      <c r="N123" s="4" t="n"/>
+      <c r="O123" s="4" t="n"/>
+      <c r="P123" s="4" t="n"/>
       <c r="Q123" s="4" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-04; 相对D0=0.66%</t>
@@ -9009,24 +7158,12 @@
       <c r="J124" s="4" t="n">
         <v>380.18</v>
       </c>
-      <c r="K124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O124" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P124" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K124" s="4" t="n"/>
+      <c r="L124" s="4" t="n"/>
+      <c r="M124" s="4" t="n"/>
+      <c r="N124" s="4" t="n"/>
+      <c r="O124" s="4" t="n"/>
+      <c r="P124" s="4" t="n"/>
       <c r="Q124" s="4" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-04; 相对D0=16.73%</t>
@@ -9078,24 +7215,12 @@
       <c r="J125" s="4" t="n">
         <v>428.05</v>
       </c>
-      <c r="K125" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L125" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M125" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N125" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O125" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P125" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K125" s="4" t="n"/>
+      <c r="L125" s="4" t="n"/>
+      <c r="M125" s="4" t="n"/>
+      <c r="N125" s="4" t="n"/>
+      <c r="O125" s="4" t="n"/>
+      <c r="P125" s="4" t="n"/>
       <c r="Q125" s="4" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-04; 相对D0=0.25%</t>
@@ -9147,24 +7272,6 @@
       <c r="J126" t="n">
         <v>259.67</v>
       </c>
-      <c r="K126" t="n">
-        <v/>
-      </c>
-      <c r="L126" t="n">
-        <v/>
-      </c>
-      <c r="M126" t="n">
-        <v/>
-      </c>
-      <c r="N126" t="n">
-        <v/>
-      </c>
-      <c r="O126" t="n">
-        <v/>
-      </c>
-      <c r="P126" t="n">
-        <v/>
-      </c>
       <c r="Q126" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-04; 相对D0=14.73%</t>
@@ -9216,24 +7323,12 @@
       <c r="J127" s="4" t="n">
         <v>131.57</v>
       </c>
-      <c r="K127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O127" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P127" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K127" s="4" t="n"/>
+      <c r="L127" s="4" t="n"/>
+      <c r="M127" s="4" t="n"/>
+      <c r="N127" s="4" t="n"/>
+      <c r="O127" s="4" t="n"/>
+      <c r="P127" s="4" t="n"/>
       <c r="Q127" s="4" t="inlineStr">
         <is>
           <t>D0=133.31; 最新=2026-06-04; 相对D0=-1.31%</t>
@@ -9285,24 +7380,6 @@
       <c r="J128" t="n">
         <v>123.48</v>
       </c>
-      <c r="K128" t="n">
-        <v/>
-      </c>
-      <c r="L128" t="n">
-        <v/>
-      </c>
-      <c r="M128" t="n">
-        <v/>
-      </c>
-      <c r="N128" t="n">
-        <v/>
-      </c>
-      <c r="O128" t="n">
-        <v/>
-      </c>
-      <c r="P128" t="n">
-        <v/>
-      </c>
       <c r="Q128" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-04; 相对D0=30.36%</t>
@@ -9354,24 +7431,12 @@
       <c r="J129" s="4" t="n">
         <v>141.7</v>
       </c>
-      <c r="K129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O129" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P129" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K129" s="4" t="n"/>
+      <c r="L129" s="4" t="n"/>
+      <c r="M129" s="4" t="n"/>
+      <c r="N129" s="4" t="n"/>
+      <c r="O129" s="4" t="n"/>
+      <c r="P129" s="4" t="n"/>
       <c r="Q129" s="4" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-04; 相对D0=-1.14%</t>
@@ -9423,24 +7488,12 @@
       <c r="J130" s="4" t="n">
         <v>181.16</v>
       </c>
-      <c r="K130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O130" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P130" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K130" s="4" t="n"/>
+      <c r="L130" s="4" t="n"/>
+      <c r="M130" s="4" t="n"/>
+      <c r="N130" s="4" t="n"/>
+      <c r="O130" s="4" t="n"/>
+      <c r="P130" s="4" t="n"/>
       <c r="Q130" s="4" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-04; 相对D0=5.53%</t>
@@ -9492,24 +7545,12 @@
       <c r="J131" s="4" t="n">
         <v>264.59</v>
       </c>
-      <c r="K131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O131" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P131" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K131" s="4" t="n"/>
+      <c r="L131" s="4" t="n"/>
+      <c r="M131" s="4" t="n"/>
+      <c r="N131" s="4" t="n"/>
+      <c r="O131" s="4" t="n"/>
+      <c r="P131" s="4" t="n"/>
       <c r="Q131" s="4" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-04; 相对D0=-8.05%</t>
@@ -9561,24 +7602,6 @@
       <c r="J132" t="n">
         <v>164.13</v>
       </c>
-      <c r="K132" t="n">
-        <v/>
-      </c>
-      <c r="L132" t="n">
-        <v/>
-      </c>
-      <c r="M132" t="n">
-        <v/>
-      </c>
-      <c r="N132" t="n">
-        <v/>
-      </c>
-      <c r="O132" t="n">
-        <v/>
-      </c>
-      <c r="P132" t="n">
-        <v/>
-      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>D0=189.03; 最新=2026-06-04; 相对D0=-13.17%</t>
@@ -9630,24 +7653,12 @@
       <c r="J133" s="4" t="n">
         <v>188.75</v>
       </c>
-      <c r="K133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O133" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P133" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K133" s="4" t="n"/>
+      <c r="L133" s="4" t="n"/>
+      <c r="M133" s="4" t="n"/>
+      <c r="N133" s="4" t="n"/>
+      <c r="O133" s="4" t="n"/>
+      <c r="P133" s="4" t="n"/>
       <c r="Q133" s="4" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-04; 相对D0=-1.23%</t>
@@ -9699,24 +7710,6 @@
       <c r="J134" t="n">
         <v>108.03</v>
       </c>
-      <c r="K134" t="n">
-        <v/>
-      </c>
-      <c r="L134" t="n">
-        <v/>
-      </c>
-      <c r="M134" t="n">
-        <v/>
-      </c>
-      <c r="N134" t="n">
-        <v/>
-      </c>
-      <c r="O134" t="n">
-        <v/>
-      </c>
-      <c r="P134" t="n">
-        <v/>
-      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>D0=109.53; 最新=2026-06-04; 相对D0=-1.37%</t>
@@ -9768,24 +7761,12 @@
       <c r="J135" s="4" t="n">
         <v>47.65</v>
       </c>
-      <c r="K135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O135" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P135" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K135" s="4" t="n"/>
+      <c r="L135" s="4" t="n"/>
+      <c r="M135" s="4" t="n"/>
+      <c r="N135" s="4" t="n"/>
+      <c r="O135" s="4" t="n"/>
+      <c r="P135" s="4" t="n"/>
       <c r="Q135" s="4" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-04; 相对D0=-1.59%</t>
@@ -9837,24 +7818,6 @@
       <c r="J136" t="n">
         <v>2131.1001</v>
       </c>
-      <c r="K136" t="n">
-        <v/>
-      </c>
-      <c r="L136" t="n">
-        <v/>
-      </c>
-      <c r="M136" t="n">
-        <v/>
-      </c>
-      <c r="N136" t="n">
-        <v/>
-      </c>
-      <c r="O136" t="n">
-        <v/>
-      </c>
-      <c r="P136" t="n">
-        <v/>
-      </c>
       <c r="Q136" t="inlineStr">
         <is>
           <t>D0=1921.71; 最新=2026-06-04; 相对D0=10.90%</t>
@@ -9906,24 +7869,12 @@
       <c r="J137" s="4" t="n">
         <v>380.18</v>
       </c>
-      <c r="K137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O137" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P137" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="n"/>
+      <c r="M137" s="4" t="n"/>
+      <c r="N137" s="4" t="n"/>
+      <c r="O137" s="4" t="n"/>
+      <c r="P137" s="4" t="n"/>
       <c r="Q137" s="4" t="inlineStr">
         <is>
           <t>D0=335.55; 最新=2026-06-04; 相对D0=13.30%</t>
@@ -9975,24 +7926,12 @@
       <c r="J138" s="4" t="n">
         <v>406.86</v>
       </c>
-      <c r="K138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O138" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P138" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K138" s="4" t="n"/>
+      <c r="L138" s="4" t="n"/>
+      <c r="M138" s="4" t="n"/>
+      <c r="N138" s="4" t="n"/>
+      <c r="O138" s="4" t="n"/>
+      <c r="P138" s="4" t="n"/>
       <c r="Q138" s="4" t="inlineStr">
         <is>
           <t>D0=374.31; 最新=2026-06-04; 相对D0=8.70%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -10044,24 +7983,12 @@
       <c r="J139" s="4" t="n">
         <v>14.14</v>
       </c>
-      <c r="K139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O139" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P139" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K139" s="4" t="n"/>
+      <c r="L139" s="4" t="n"/>
+      <c r="M139" s="4" t="n"/>
+      <c r="N139" s="4" t="n"/>
+      <c r="O139" s="4" t="n"/>
+      <c r="P139" s="4" t="n"/>
       <c r="Q139" s="4" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-04; 相对D0=2.69%</t>
@@ -10113,24 +8040,12 @@
       <c r="J140" s="4" t="n">
         <v>202.89</v>
       </c>
-      <c r="K140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O140" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P140" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K140" s="4" t="n"/>
+      <c r="L140" s="4" t="n"/>
+      <c r="M140" s="4" t="n"/>
+      <c r="N140" s="4" t="n"/>
+      <c r="O140" s="4" t="n"/>
+      <c r="P140" s="4" t="n"/>
       <c r="Q140" s="4" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-04; 相对D0=9.27%</t>
@@ -10182,24 +8097,6 @@
       <c r="J141" t="n">
         <v>14.73</v>
       </c>
-      <c r="K141" t="n">
-        <v/>
-      </c>
-      <c r="L141" t="n">
-        <v/>
-      </c>
-      <c r="M141" t="n">
-        <v/>
-      </c>
-      <c r="N141" t="n">
-        <v/>
-      </c>
-      <c r="O141" t="n">
-        <v/>
-      </c>
-      <c r="P141" t="n">
-        <v/>
-      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-04; 相对D0=0.20%</t>
@@ -10251,24 +8148,12 @@
       <c r="J142" s="4" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="K142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O142" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P142" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K142" s="4" t="n"/>
+      <c r="L142" s="4" t="n"/>
+      <c r="M142" s="4" t="n"/>
+      <c r="N142" s="4" t="n"/>
+      <c r="O142" s="4" t="n"/>
+      <c r="P142" s="4" t="n"/>
       <c r="Q142" s="4" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-04; 相对D0=1.47%</t>
@@ -10320,24 +8205,6 @@
       <c r="J143" t="n">
         <v>119.23</v>
       </c>
-      <c r="K143" t="n">
-        <v/>
-      </c>
-      <c r="L143" t="n">
-        <v/>
-      </c>
-      <c r="M143" t="n">
-        <v/>
-      </c>
-      <c r="N143" t="n">
-        <v/>
-      </c>
-      <c r="O143" t="n">
-        <v/>
-      </c>
-      <c r="P143" t="n">
-        <v/>
-      </c>
       <c r="Q143" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-04; 相对D0=3.16%; 历史重复2次; 重复日期=2026-06-02, 2026-06-03</t>
@@ -10389,24 +8256,6 @@
       <c r="J144" t="n">
         <v>188.35</v>
       </c>
-      <c r="K144" t="n">
-        <v/>
-      </c>
-      <c r="L144" t="n">
-        <v/>
-      </c>
-      <c r="M144" t="n">
-        <v/>
-      </c>
-      <c r="N144" t="n">
-        <v/>
-      </c>
-      <c r="O144" t="n">
-        <v/>
-      </c>
-      <c r="P144" t="n">
-        <v/>
-      </c>
       <c r="Q144" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-04; 相对D0=1.36%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -10458,24 +8307,6 @@
       <c r="J145" t="n">
         <v>140.88</v>
       </c>
-      <c r="K145" t="n">
-        <v/>
-      </c>
-      <c r="L145" t="n">
-        <v/>
-      </c>
-      <c r="M145" t="n">
-        <v/>
-      </c>
-      <c r="N145" t="n">
-        <v/>
-      </c>
-      <c r="O145" t="n">
-        <v/>
-      </c>
-      <c r="P145" t="n">
-        <v/>
-      </c>
       <c r="Q145" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-04; 相对D0=3.12%</t>
@@ -10527,24 +8358,6 @@
       <c r="J146" t="n">
         <v>8.08</v>
       </c>
-      <c r="K146" t="n">
-        <v/>
-      </c>
-      <c r="L146" t="n">
-        <v/>
-      </c>
-      <c r="M146" t="n">
-        <v/>
-      </c>
-      <c r="N146" t="n">
-        <v/>
-      </c>
-      <c r="O146" t="n">
-        <v/>
-      </c>
-      <c r="P146" t="n">
-        <v/>
-      </c>
       <c r="Q146" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-04; 相对D0=-9.92%</t>
@@ -10596,24 +8409,6 @@
       <c r="J147" t="n">
         <v>27.15</v>
       </c>
-      <c r="K147" t="n">
-        <v/>
-      </c>
-      <c r="L147" t="n">
-        <v/>
-      </c>
-      <c r="M147" t="n">
-        <v/>
-      </c>
-      <c r="N147" t="n">
-        <v/>
-      </c>
-      <c r="O147" t="n">
-        <v/>
-      </c>
-      <c r="P147" t="n">
-        <v/>
-      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-04; 相对D0=0.00%</t>
@@ -10665,24 +8460,6 @@
       <c r="J148" t="n">
         <v>51.58</v>
       </c>
-      <c r="K148" t="n">
-        <v/>
-      </c>
-      <c r="L148" t="n">
-        <v/>
-      </c>
-      <c r="M148" t="n">
-        <v/>
-      </c>
-      <c r="N148" t="n">
-        <v/>
-      </c>
-      <c r="O148" t="n">
-        <v/>
-      </c>
-      <c r="P148" t="n">
-        <v/>
-      </c>
       <c r="Q148" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-04; 相对D0=2.04%</t>
@@ -10734,24 +8511,12 @@
       <c r="J149" s="4" t="n">
         <v>186.69</v>
       </c>
-      <c r="K149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O149" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P149" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K149" s="4" t="n"/>
+      <c r="L149" s="4" t="n"/>
+      <c r="M149" s="4" t="n"/>
+      <c r="N149" s="4" t="n"/>
+      <c r="O149" s="4" t="n"/>
+      <c r="P149" s="4" t="n"/>
       <c r="Q149" s="4" t="inlineStr">
         <is>
           <t>D0=189.00; 最新=2026-06-04; 相对D0=-1.22%</t>
@@ -10803,24 +8568,12 @@
       <c r="J150" s="4" t="n">
         <v>12.18</v>
       </c>
-      <c r="K150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O150" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P150" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K150" s="4" t="n"/>
+      <c r="L150" s="4" t="n"/>
+      <c r="M150" s="4" t="n"/>
+      <c r="N150" s="4" t="n"/>
+      <c r="O150" s="4" t="n"/>
+      <c r="P150" s="4" t="n"/>
       <c r="Q150" s="4" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-04; 相对D0=10.53%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -10872,24 +8625,6 @@
       <c r="J151" t="n">
         <v>69</v>
       </c>
-      <c r="K151" t="n">
-        <v/>
-      </c>
-      <c r="L151" t="n">
-        <v/>
-      </c>
-      <c r="M151" t="n">
-        <v/>
-      </c>
-      <c r="N151" t="n">
-        <v/>
-      </c>
-      <c r="O151" t="n">
-        <v/>
-      </c>
-      <c r="P151" t="n">
-        <v/>
-      </c>
       <c r="Q151" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-04; 相对D0=-0.82%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -10941,24 +8676,12 @@
       <c r="J152" s="4" t="n">
         <v>218.66</v>
       </c>
-      <c r="K152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O152" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P152" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K152" s="4" t="n"/>
+      <c r="L152" s="4" t="n"/>
+      <c r="M152" s="4" t="n"/>
+      <c r="N152" s="4" t="n"/>
+      <c r="O152" s="4" t="n"/>
+      <c r="P152" s="4" t="n"/>
       <c r="Q152" s="4" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-04; 相对D0=-2.54%</t>
@@ -11010,24 +8733,12 @@
       <c r="J153" s="4" t="n">
         <v>65.39</v>
       </c>
-      <c r="K153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O153" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P153" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K153" s="4" t="n"/>
+      <c r="L153" s="4" t="n"/>
+      <c r="M153" s="4" t="n"/>
+      <c r="N153" s="4" t="n"/>
+      <c r="O153" s="4" t="n"/>
+      <c r="P153" s="4" t="n"/>
       <c r="Q153" s="4" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-04; 相对D0=-2.24%</t>
@@ -11079,24 +8790,6 @@
       <c r="J154" t="n">
         <v>58.67</v>
       </c>
-      <c r="K154" t="n">
-        <v/>
-      </c>
-      <c r="L154" t="n">
-        <v/>
-      </c>
-      <c r="M154" t="n">
-        <v/>
-      </c>
-      <c r="N154" t="n">
-        <v/>
-      </c>
-      <c r="O154" t="n">
-        <v/>
-      </c>
-      <c r="P154" t="n">
-        <v/>
-      </c>
       <c r="Q154" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-04; 相对D0=-0.42%</t>
@@ -11148,24 +8841,12 @@
       <c r="J155" s="4" t="n">
         <v>15.475</v>
       </c>
-      <c r="K155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O155" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P155" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K155" s="4" t="n"/>
+      <c r="L155" s="4" t="n"/>
+      <c r="M155" s="4" t="n"/>
+      <c r="N155" s="4" t="n"/>
+      <c r="O155" s="4" t="n"/>
+      <c r="P155" s="4" t="n"/>
       <c r="Q155" s="4" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-04; 相对D0=11.41%</t>
@@ -11217,24 +8898,6 @@
       <c r="J156" t="n">
         <v>14.82</v>
       </c>
-      <c r="K156" t="n">
-        <v/>
-      </c>
-      <c r="L156" t="n">
-        <v/>
-      </c>
-      <c r="M156" t="n">
-        <v/>
-      </c>
-      <c r="N156" t="n">
-        <v/>
-      </c>
-      <c r="O156" t="n">
-        <v/>
-      </c>
-      <c r="P156" t="n">
-        <v/>
-      </c>
       <c r="Q156" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-04; 相对D0=-4.88%</t>
@@ -11286,24 +8949,12 @@
       <c r="J157" s="4" t="n">
         <v>17.37</v>
       </c>
-      <c r="K157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O157" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P157" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K157" s="4" t="n"/>
+      <c r="L157" s="4" t="n"/>
+      <c r="M157" s="4" t="n"/>
+      <c r="N157" s="4" t="n"/>
+      <c r="O157" s="4" t="n"/>
+      <c r="P157" s="4" t="n"/>
       <c r="Q157" s="4" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-04; 相对D0=-1.42%</t>
@@ -11355,24 +9006,6 @@
       <c r="J158" t="n">
         <v>323.92</v>
       </c>
-      <c r="K158" t="n">
-        <v/>
-      </c>
-      <c r="L158" t="n">
-        <v/>
-      </c>
-      <c r="M158" t="n">
-        <v/>
-      </c>
-      <c r="N158" t="n">
-        <v/>
-      </c>
-      <c r="O158" t="n">
-        <v/>
-      </c>
-      <c r="P158" t="n">
-        <v/>
-      </c>
       <c r="Q158" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-04; 相对D0=0.16%</t>
@@ -11424,24 +9057,6 @@
       <c r="J159" t="n">
         <v>135.26</v>
       </c>
-      <c r="K159" t="n">
-        <v/>
-      </c>
-      <c r="L159" t="n">
-        <v/>
-      </c>
-      <c r="M159" t="n">
-        <v/>
-      </c>
-      <c r="N159" t="n">
-        <v/>
-      </c>
-      <c r="O159" t="n">
-        <v/>
-      </c>
-      <c r="P159" t="n">
-        <v/>
-      </c>
       <c r="Q159" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-04; 相对D0=-13.13%</t>
@@ -11493,24 +9108,12 @@
       <c r="J160" s="4" t="n">
         <v>311.23</v>
       </c>
-      <c r="K160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O160" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P160" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K160" s="4" t="n"/>
+      <c r="L160" s="4" t="n"/>
+      <c r="M160" s="4" t="n"/>
+      <c r="N160" s="4" t="n"/>
+      <c r="O160" s="4" t="n"/>
+      <c r="P160" s="4" t="n"/>
       <c r="Q160" s="4" t="inlineStr">
         <is>
           <t>D0=315.20; 最新=2026-06-04; 相对D0=-1.26%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -11562,24 +9165,12 @@
       <c r="J161" s="4" t="n">
         <v>116.58</v>
       </c>
-      <c r="K161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O161" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P161" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K161" s="4" t="n"/>
+      <c r="L161" s="4" t="n"/>
+      <c r="M161" s="4" t="n"/>
+      <c r="N161" s="4" t="n"/>
+      <c r="O161" s="4" t="n"/>
+      <c r="P161" s="4" t="n"/>
       <c r="Q161" s="4" t="inlineStr">
         <is>
           <t>D0=113.00; 最新=2026-06-04; 相对D0=3.17%</t>
@@ -11631,24 +9222,6 @@
       <c r="J162" t="n">
         <v>107.29</v>
       </c>
-      <c r="K162" t="n">
-        <v/>
-      </c>
-      <c r="L162" t="n">
-        <v/>
-      </c>
-      <c r="M162" t="n">
-        <v/>
-      </c>
-      <c r="N162" t="n">
-        <v/>
-      </c>
-      <c r="O162" t="n">
-        <v/>
-      </c>
-      <c r="P162" t="n">
-        <v/>
-      </c>
       <c r="Q162" t="inlineStr">
         <is>
           <t>D0=118.17; 最新=2026-06-04; 相对D0=-9.21%</t>
@@ -11700,24 +9273,6 @@
       <c r="J163" t="n">
         <v>291.37</v>
       </c>
-      <c r="K163" t="n">
-        <v/>
-      </c>
-      <c r="L163" t="n">
-        <v/>
-      </c>
-      <c r="M163" t="n">
-        <v/>
-      </c>
-      <c r="N163" t="n">
-        <v/>
-      </c>
-      <c r="O163" t="n">
-        <v/>
-      </c>
-      <c r="P163" t="n">
-        <v/>
-      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>D0=302.85; 最新=2026-06-04; 相对D0=-3.79%</t>
@@ -11769,24 +9324,12 @@
       <c r="J164" s="4" t="n">
         <v>181.16</v>
       </c>
-      <c r="K164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O164" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P164" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K164" s="4" t="n"/>
+      <c r="L164" s="4" t="n"/>
+      <c r="M164" s="4" t="n"/>
+      <c r="N164" s="4" t="n"/>
+      <c r="O164" s="4" t="n"/>
+      <c r="P164" s="4" t="n"/>
       <c r="Q164" s="4" t="inlineStr">
         <is>
           <t>D0=187.52; 最新=2026-06-04; 相对D0=-3.39%</t>
@@ -11838,24 +9381,12 @@
       <c r="J165" s="4" t="n">
         <v>421.9</v>
       </c>
-      <c r="K165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O165" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P165" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K165" s="4" t="n"/>
+      <c r="L165" s="4" t="n"/>
+      <c r="M165" s="4" t="n"/>
+      <c r="N165" s="4" t="n"/>
+      <c r="O165" s="4" t="n"/>
+      <c r="P165" s="4" t="n"/>
       <c r="Q165" s="4" t="inlineStr">
         <is>
           <t>D0=426.89; 最新=2026-06-04; 相对D0=-1.17%</t>
@@ -11907,24 +9438,6 @@
       <c r="J166" t="n">
         <v>119.23</v>
       </c>
-      <c r="K166" t="n">
-        <v/>
-      </c>
-      <c r="L166" t="n">
-        <v/>
-      </c>
-      <c r="M166" t="n">
-        <v/>
-      </c>
-      <c r="N166" t="n">
-        <v/>
-      </c>
-      <c r="O166" t="n">
-        <v/>
-      </c>
-      <c r="P166" t="n">
-        <v/>
-      </c>
       <c r="Q166" t="inlineStr">
         <is>
           <t>D0=116.87; 最新=2026-06-04; 相对D0=2.02%</t>
@@ -11976,24 +9489,6 @@
       <c r="J167" t="n">
         <v>188.35</v>
       </c>
-      <c r="K167" t="n">
-        <v/>
-      </c>
-      <c r="L167" t="n">
-        <v/>
-      </c>
-      <c r="M167" t="n">
-        <v/>
-      </c>
-      <c r="N167" t="n">
-        <v/>
-      </c>
-      <c r="O167" t="n">
-        <v/>
-      </c>
-      <c r="P167" t="n">
-        <v/>
-      </c>
       <c r="Q167" t="inlineStr">
         <is>
           <t>D0=187.55; 最新=2026-06-04; 相对D0=0.43%</t>
@@ -12045,24 +9540,6 @@
       <c r="J168" t="n">
         <v>66.5</v>
       </c>
-      <c r="K168" t="n">
-        <v/>
-      </c>
-      <c r="L168" t="n">
-        <v/>
-      </c>
-      <c r="M168" t="n">
-        <v/>
-      </c>
-      <c r="N168" t="n">
-        <v/>
-      </c>
-      <c r="O168" t="n">
-        <v/>
-      </c>
-      <c r="P168" t="n">
-        <v/>
-      </c>
       <c r="Q168" t="inlineStr">
         <is>
           <t>D0=66.47; 最新=2026-06-04; 相对D0=0.05%</t>
@@ -12114,24 +9591,12 @@
       <c r="J169" s="4" t="n">
         <v>47.65</v>
       </c>
-      <c r="K169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O169" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P169" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K169" s="4" t="n"/>
+      <c r="L169" s="4" t="n"/>
+      <c r="M169" s="4" t="n"/>
+      <c r="N169" s="4" t="n"/>
+      <c r="O169" s="4" t="n"/>
+      <c r="P169" s="4" t="n"/>
       <c r="Q169" s="4" t="inlineStr">
         <is>
           <t>D0=48.66; 最新=2026-06-04; 相对D0=-2.08%</t>
@@ -12183,24 +9648,6 @@
       <c r="J170" t="n">
         <v>68.39</v>
       </c>
-      <c r="K170" t="n">
-        <v/>
-      </c>
-      <c r="L170" t="n">
-        <v/>
-      </c>
-      <c r="M170" t="n">
-        <v/>
-      </c>
-      <c r="N170" t="n">
-        <v/>
-      </c>
-      <c r="O170" t="n">
-        <v/>
-      </c>
-      <c r="P170" t="n">
-        <v/>
-      </c>
       <c r="Q170" t="inlineStr">
         <is>
           <t>D0=72.33; 最新=2026-06-04; 相对D0=-5.45%</t>
@@ -12252,24 +9699,12 @@
       <c r="J171" s="4" t="n">
         <v>139.88</v>
       </c>
-      <c r="K171" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L171" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M171" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N171" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O171" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P171" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K171" s="4" t="n"/>
+      <c r="L171" s="4" t="n"/>
+      <c r="M171" s="4" t="n"/>
+      <c r="N171" s="4" t="n"/>
+      <c r="O171" s="4" t="n"/>
+      <c r="P171" s="4" t="n"/>
       <c r="Q171" s="4" t="inlineStr">
         <is>
           <t>D0=142.92; 最新=2026-06-04; 相对D0=-2.13%</t>
@@ -12321,24 +9756,6 @@
       <c r="J172" t="n">
         <v>140.88</v>
       </c>
-      <c r="K172" t="n">
-        <v/>
-      </c>
-      <c r="L172" t="n">
-        <v/>
-      </c>
-      <c r="M172" t="n">
-        <v/>
-      </c>
-      <c r="N172" t="n">
-        <v/>
-      </c>
-      <c r="O172" t="n">
-        <v/>
-      </c>
-      <c r="P172" t="n">
-        <v/>
-      </c>
       <c r="Q172" t="inlineStr">
         <is>
           <t>D0=138.58; 最新=2026-06-04; 相对D0=1.66%</t>
@@ -12390,24 +9807,6 @@
       <c r="J173" t="n">
         <v>418.61</v>
       </c>
-      <c r="K173" t="n">
-        <v/>
-      </c>
-      <c r="L173" t="n">
-        <v/>
-      </c>
-      <c r="M173" t="n">
-        <v/>
-      </c>
-      <c r="N173" t="n">
-        <v/>
-      </c>
-      <c r="O173" t="n">
-        <v/>
-      </c>
-      <c r="P173" t="n">
-        <v/>
-      </c>
       <c r="Q173" t="inlineStr">
         <is>
           <t>D0=417.62; 最新=2026-06-04; 相对D0=0.24%</t>
@@ -12459,24 +9858,12 @@
       <c r="J174" s="4" t="n">
         <v>197.7</v>
       </c>
-      <c r="K174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O174" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P174" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K174" s="4" t="n"/>
+      <c r="L174" s="4" t="n"/>
+      <c r="M174" s="4" t="n"/>
+      <c r="N174" s="4" t="n"/>
+      <c r="O174" s="4" t="n"/>
+      <c r="P174" s="4" t="n"/>
       <c r="Q174" s="4" t="inlineStr">
         <is>
           <t>D0=200.40; 最新=2026-06-04; 相对D0=-1.35%</t>
@@ -12528,24 +9915,6 @@
       <c r="J175" t="n">
         <v>41.22</v>
       </c>
-      <c r="K175" t="n">
-        <v/>
-      </c>
-      <c r="L175" t="n">
-        <v/>
-      </c>
-      <c r="M175" t="n">
-        <v/>
-      </c>
-      <c r="N175" t="n">
-        <v/>
-      </c>
-      <c r="O175" t="n">
-        <v/>
-      </c>
-      <c r="P175" t="n">
-        <v/>
-      </c>
       <c r="Q175" t="inlineStr">
         <is>
           <t>D0=40.13; 最新=2026-06-04; 相对D0=2.72%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -12597,24 +9966,12 @@
       <c r="J176" s="4" t="n">
         <v>12.18</v>
       </c>
-      <c r="K176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O176" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P176" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K176" s="4" t="n"/>
+      <c r="L176" s="4" t="n"/>
+      <c r="M176" s="4" t="n"/>
+      <c r="N176" s="4" t="n"/>
+      <c r="O176" s="4" t="n"/>
+      <c r="P176" s="4" t="n"/>
       <c r="Q176" s="4" t="inlineStr">
         <is>
           <t>D0=12.72; 最新=2026-06-04; 相对D0=-4.25%</t>
@@ -12666,24 +10023,6 @@
       <c r="J177" t="n">
         <v>22.9</v>
       </c>
-      <c r="K177" t="n">
-        <v/>
-      </c>
-      <c r="L177" t="n">
-        <v/>
-      </c>
-      <c r="M177" t="n">
-        <v/>
-      </c>
-      <c r="N177" t="n">
-        <v/>
-      </c>
-      <c r="O177" t="n">
-        <v/>
-      </c>
-      <c r="P177" t="n">
-        <v/>
-      </c>
       <c r="Q177" t="inlineStr">
         <is>
           <t>D0=23.30; 最新=2026-06-04; 相对D0=-1.72%</t>
@@ -12735,24 +10074,12 @@
       <c r="J178" s="4" t="n">
         <v>131.57</v>
       </c>
-      <c r="K178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O178" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P178" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K178" s="4" t="n"/>
+      <c r="L178" s="4" t="n"/>
+      <c r="M178" s="4" t="n"/>
+      <c r="N178" s="4" t="n"/>
+      <c r="O178" s="4" t="n"/>
+      <c r="P178" s="4" t="n"/>
       <c r="Q178" s="4" t="inlineStr">
         <is>
           <t>D0=138.17; 最新=2026-06-04; 相对D0=-4.78%</t>
@@ -12804,24 +10131,6 @@
       <c r="J179" t="n">
         <v>133.39</v>
       </c>
-      <c r="K179" t="n">
-        <v/>
-      </c>
-      <c r="L179" t="n">
-        <v/>
-      </c>
-      <c r="M179" t="n">
-        <v/>
-      </c>
-      <c r="N179" t="n">
-        <v/>
-      </c>
-      <c r="O179" t="n">
-        <v/>
-      </c>
-      <c r="P179" t="n">
-        <v/>
-      </c>
       <c r="Q179" t="inlineStr">
         <is>
           <t>D0=133.51; 最新=2026-06-04; 相对D0=-0.09%</t>
@@ -12873,24 +10182,6 @@
       <c r="J180" t="n">
         <v>30.67</v>
       </c>
-      <c r="K180" t="n">
-        <v/>
-      </c>
-      <c r="L180" t="n">
-        <v/>
-      </c>
-      <c r="M180" t="n">
-        <v/>
-      </c>
-      <c r="N180" t="n">
-        <v/>
-      </c>
-      <c r="O180" t="n">
-        <v/>
-      </c>
-      <c r="P180" t="n">
-        <v/>
-      </c>
       <c r="Q180" t="inlineStr">
         <is>
           <t>D0=25.86; 最新=2026-06-04; 相对D0=18.60%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -12942,24 +10233,12 @@
       <c r="J181" s="4" t="n">
         <v>65.39</v>
       </c>
-      <c r="K181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O181" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P181" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K181" s="4" t="n"/>
+      <c r="L181" s="4" t="n"/>
+      <c r="M181" s="4" t="n"/>
+      <c r="N181" s="4" t="n"/>
+      <c r="O181" s="4" t="n"/>
+      <c r="P181" s="4" t="n"/>
       <c r="Q181" s="4" t="inlineStr">
         <is>
           <t>D0=73.47; 最新=2026-06-04; 相对D0=-11.00%</t>
@@ -13011,24 +10290,12 @@
       <c r="J182" s="4" t="n">
         <v>274.76</v>
       </c>
-      <c r="K182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O182" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P182" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K182" s="4" t="n"/>
+      <c r="L182" s="4" t="n"/>
+      <c r="M182" s="4" t="n"/>
+      <c r="N182" s="4" t="n"/>
+      <c r="O182" s="4" t="n"/>
+      <c r="P182" s="4" t="n"/>
       <c r="Q182" s="4" t="inlineStr">
         <is>
           <t>D0=278.02; 最新=2026-06-04; 相对D0=-1.17%</t>
@@ -13080,24 +10347,6 @@
       <c r="J183" t="n">
         <v>57.61</v>
       </c>
-      <c r="K183" t="n">
-        <v/>
-      </c>
-      <c r="L183" t="n">
-        <v/>
-      </c>
-      <c r="M183" t="n">
-        <v/>
-      </c>
-      <c r="N183" t="n">
-        <v/>
-      </c>
-      <c r="O183" t="n">
-        <v/>
-      </c>
-      <c r="P183" t="n">
-        <v/>
-      </c>
       <c r="Q183" t="inlineStr">
         <is>
           <t>D0=56.89; 最新=2026-06-04; 相对D0=1.27%</t>
@@ -13149,24 +10398,6 @@
       <c r="J184" t="n">
         <v>58.01</v>
       </c>
-      <c r="K184" t="n">
-        <v/>
-      </c>
-      <c r="L184" t="n">
-        <v/>
-      </c>
-      <c r="M184" t="n">
-        <v/>
-      </c>
-      <c r="N184" t="n">
-        <v/>
-      </c>
-      <c r="O184" t="n">
-        <v/>
-      </c>
-      <c r="P184" t="n">
-        <v/>
-      </c>
       <c r="Q184" t="inlineStr">
         <is>
           <t>D0=56.56; 最新=2026-06-04; 相对D0=2.56%</t>
@@ -13218,24 +10449,6 @@
       <c r="J185" t="n">
         <v>494.48</v>
       </c>
-      <c r="K185" t="n">
-        <v/>
-      </c>
-      <c r="L185" t="n">
-        <v/>
-      </c>
-      <c r="M185" t="n">
-        <v/>
-      </c>
-      <c r="N185" t="n">
-        <v/>
-      </c>
-      <c r="O185" t="n">
-        <v/>
-      </c>
-      <c r="P185" t="n">
-        <v/>
-      </c>
       <c r="Q185" t="inlineStr">
         <is>
           <t>D0=508.35; 最新=2026-06-04; 相对D0=-2.73%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -13287,24 +10500,6 @@
       <c r="J186" t="n">
         <v>84.13</v>
       </c>
-      <c r="K186" t="n">
-        <v/>
-      </c>
-      <c r="L186" t="n">
-        <v/>
-      </c>
-      <c r="M186" t="n">
-        <v/>
-      </c>
-      <c r="N186" t="n">
-        <v/>
-      </c>
-      <c r="O186" t="n">
-        <v/>
-      </c>
-      <c r="P186" t="n">
-        <v/>
-      </c>
       <c r="Q186" t="inlineStr">
         <is>
           <t>D0=87.39; 最新=2026-06-04; 相对D0=-3.73%</t>
@@ -13356,24 +10551,12 @@
       <c r="J187" s="4" t="n">
         <v>406.86</v>
       </c>
-      <c r="K187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O187" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P187" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K187" s="4" t="n"/>
+      <c r="L187" s="4" t="n"/>
+      <c r="M187" s="4" t="n"/>
+      <c r="N187" s="4" t="n"/>
+      <c r="O187" s="4" t="n"/>
+      <c r="P187" s="4" t="n"/>
       <c r="Q187" s="4" t="inlineStr">
         <is>
           <t>D0=392.62; 最新=2026-06-04; 相对D0=3.63%</t>
@@ -13425,24 +10608,6 @@
       <c r="J188" t="n">
         <v>378.08</v>
       </c>
-      <c r="K188" t="n">
-        <v/>
-      </c>
-      <c r="L188" t="n">
-        <v/>
-      </c>
-      <c r="M188" t="n">
-        <v/>
-      </c>
-      <c r="N188" t="n">
-        <v/>
-      </c>
-      <c r="O188" t="n">
-        <v/>
-      </c>
-      <c r="P188" t="n">
-        <v/>
-      </c>
       <c r="Q188" t="inlineStr">
         <is>
           <t>D0=385.51; 最新=2026-06-04; 相对D0=-1.93%</t>
@@ -13494,24 +10659,12 @@
       <c r="J189" s="4" t="n">
         <v>261.31</v>
       </c>
-      <c r="K189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O189" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P189" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K189" s="4" t="n"/>
+      <c r="L189" s="4" t="n"/>
+      <c r="M189" s="4" t="n"/>
+      <c r="N189" s="4" t="n"/>
+      <c r="O189" s="4" t="n"/>
+      <c r="P189" s="4" t="n"/>
       <c r="Q189" s="4" t="inlineStr">
         <is>
           <t>D0=274.71; 最新=2026-06-04; 相对D0=-4.88%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -13563,24 +10716,12 @@
       <c r="J190" s="4" t="n">
         <v>14.14</v>
       </c>
-      <c r="K190" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L190" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M190" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N190" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O190" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P190" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K190" s="4" t="n"/>
+      <c r="L190" s="4" t="n"/>
+      <c r="M190" s="4" t="n"/>
+      <c r="N190" s="4" t="n"/>
+      <c r="O190" s="4" t="n"/>
+      <c r="P190" s="4" t="n"/>
       <c r="Q190" s="4" t="inlineStr">
         <is>
           <t>D0=15.44; 最新=2026-06-04; 相对D0=-8.42%</t>
@@ -13632,24 +10773,12 @@
       <c r="J191" s="4" t="n">
         <v>17.37</v>
       </c>
-      <c r="K191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O191" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P191" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K191" s="4" t="n"/>
+      <c r="L191" s="4" t="n"/>
+      <c r="M191" s="4" t="n"/>
+      <c r="N191" s="4" t="n"/>
+      <c r="O191" s="4" t="n"/>
+      <c r="P191" s="4" t="n"/>
       <c r="Q191" s="4" t="inlineStr">
         <is>
           <t>D0=19.54; 最新=2026-06-04; 相对D0=-11.11%</t>
@@ -13701,24 +10830,6 @@
       <c r="J192" t="n">
         <v>323.92</v>
       </c>
-      <c r="K192" t="n">
-        <v/>
-      </c>
-      <c r="L192" t="n">
-        <v/>
-      </c>
-      <c r="M192" t="n">
-        <v/>
-      </c>
-      <c r="N192" t="n">
-        <v/>
-      </c>
-      <c r="O192" t="n">
-        <v/>
-      </c>
-      <c r="P192" t="n">
-        <v/>
-      </c>
       <c r="Q192" t="inlineStr">
         <is>
           <t>D0=334.49; 最新=2026-06-04; 相对D0=-3.16%</t>
@@ -13770,24 +10881,6 @@
       <c r="J193" t="n">
         <v>153.7</v>
       </c>
-      <c r="K193" t="n">
-        <v/>
-      </c>
-      <c r="L193" t="n">
-        <v/>
-      </c>
-      <c r="M193" t="n">
-        <v/>
-      </c>
-      <c r="N193" t="n">
-        <v/>
-      </c>
-      <c r="O193" t="n">
-        <v/>
-      </c>
-      <c r="P193" t="n">
-        <v/>
-      </c>
       <c r="Q193" t="inlineStr">
         <is>
           <t>D0=157.97; 最新=2026-06-04; 相对D0=-2.70%</t>
@@ -13839,24 +10932,6 @@
       <c r="J194" t="n">
         <v>51.62</v>
       </c>
-      <c r="K194" t="n">
-        <v/>
-      </c>
-      <c r="L194" t="n">
-        <v/>
-      </c>
-      <c r="M194" t="n">
-        <v/>
-      </c>
-      <c r="N194" t="n">
-        <v/>
-      </c>
-      <c r="O194" t="n">
-        <v/>
-      </c>
-      <c r="P194" t="n">
-        <v/>
-      </c>
       <c r="Q194" t="inlineStr">
         <is>
           <t>D0=51.52; 最新=2026-06-04; 相对D0=0.19%</t>
@@ -13908,24 +10983,6 @@
       <c r="J195" t="n">
         <v>58.75</v>
       </c>
-      <c r="K195" t="n">
-        <v/>
-      </c>
-      <c r="L195" t="n">
-        <v/>
-      </c>
-      <c r="M195" t="n">
-        <v/>
-      </c>
-      <c r="N195" t="n">
-        <v/>
-      </c>
-      <c r="O195" t="n">
-        <v/>
-      </c>
-      <c r="P195" t="n">
-        <v/>
-      </c>
       <c r="Q195" t="inlineStr">
         <is>
           <t>D0=57.96; 最新=2026-06-04; 相对D0=1.36%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -13977,24 +11034,6 @@
       <c r="J196" t="n">
         <v>52.21</v>
       </c>
-      <c r="K196" t="n">
-        <v/>
-      </c>
-      <c r="L196" t="n">
-        <v/>
-      </c>
-      <c r="M196" t="n">
-        <v/>
-      </c>
-      <c r="N196" t="n">
-        <v/>
-      </c>
-      <c r="O196" t="n">
-        <v/>
-      </c>
-      <c r="P196" t="n">
-        <v/>
-      </c>
       <c r="Q196" t="inlineStr">
         <is>
           <t>D0=51.46; 最新=2026-06-04; 相对D0=1.46%</t>
@@ -14046,24 +11085,12 @@
       <c r="J197" s="4" t="n">
         <v>202.89</v>
       </c>
-      <c r="K197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O197" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P197" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K197" s="4" t="n"/>
+      <c r="L197" s="4" t="n"/>
+      <c r="M197" s="4" t="n"/>
+      <c r="N197" s="4" t="n"/>
+      <c r="O197" s="4" t="n"/>
+      <c r="P197" s="4" t="n"/>
       <c r="Q197" s="4" t="inlineStr">
         <is>
           <t>D0=184.07; 最新=2026-06-04; 相对D0=10.22%</t>
@@ -14115,24 +11142,12 @@
       <c r="J198" s="4" t="n">
         <v>311.23</v>
       </c>
-      <c r="K198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O198" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P198" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K198" s="4" t="n"/>
+      <c r="L198" s="4" t="n"/>
+      <c r="M198" s="4" t="n"/>
+      <c r="N198" s="4" t="n"/>
+      <c r="O198" s="4" t="n"/>
+      <c r="P198" s="4" t="n"/>
       <c r="Q198" s="4" t="inlineStr">
         <is>
           <t>D0=310.26; 最新=2026-06-04; 相对D0=0.31%</t>
@@ -14184,24 +11199,6 @@
       <c r="J199" t="n">
         <v>282.85</v>
       </c>
-      <c r="K199" t="n">
-        <v/>
-      </c>
-      <c r="L199" t="n">
-        <v/>
-      </c>
-      <c r="M199" t="n">
-        <v/>
-      </c>
-      <c r="N199" t="n">
-        <v/>
-      </c>
-      <c r="O199" t="n">
-        <v/>
-      </c>
-      <c r="P199" t="n">
-        <v/>
-      </c>
       <c r="Q199" t="inlineStr">
         <is>
           <t>D0=282.27; 最新=2026-06-04; 相对D0=0.21%</t>
@@ -14253,24 +11250,6 @@
       <c r="J200" t="n">
         <v>119.23</v>
       </c>
-      <c r="K200" t="n">
-        <v/>
-      </c>
-      <c r="L200" t="n">
-        <v/>
-      </c>
-      <c r="M200" t="n">
-        <v/>
-      </c>
-      <c r="N200" t="n">
-        <v/>
-      </c>
-      <c r="O200" t="n">
-        <v/>
-      </c>
-      <c r="P200" t="n">
-        <v/>
-      </c>
       <c r="Q200" t="inlineStr">
         <is>
           <t>D0=119.05; 最新=2026-06-04; 相对D0=0.15%</t>
@@ -14322,24 +11301,6 @@
       <c r="J201" t="n">
         <v>121.82</v>
       </c>
-      <c r="K201" t="n">
-        <v/>
-      </c>
-      <c r="L201" t="n">
-        <v/>
-      </c>
-      <c r="M201" t="n">
-        <v/>
-      </c>
-      <c r="N201" t="n">
-        <v/>
-      </c>
-      <c r="O201" t="n">
-        <v/>
-      </c>
-      <c r="P201" t="n">
-        <v/>
-      </c>
       <c r="Q201" t="inlineStr">
         <is>
           <t>D0=121.04; 最新=2026-06-04; 相对D0=0.64%</t>
@@ -14391,24 +11352,6 @@
       <c r="J202" t="n">
         <v>41.22</v>
       </c>
-      <c r="K202" t="n">
-        <v/>
-      </c>
-      <c r="L202" t="n">
-        <v/>
-      </c>
-      <c r="M202" t="n">
-        <v/>
-      </c>
-      <c r="N202" t="n">
-        <v/>
-      </c>
-      <c r="O202" t="n">
-        <v/>
-      </c>
-      <c r="P202" t="n">
-        <v/>
-      </c>
       <c r="Q202" t="inlineStr">
         <is>
           <t>D0=41.03; 最新=2026-06-04; 相对D0=0.46%</t>
@@ -14460,24 +11403,6 @@
       <c r="J203" t="n">
         <v>51.58</v>
       </c>
-      <c r="K203" t="n">
-        <v/>
-      </c>
-      <c r="L203" t="n">
-        <v/>
-      </c>
-      <c r="M203" t="n">
-        <v/>
-      </c>
-      <c r="N203" t="n">
-        <v/>
-      </c>
-      <c r="O203" t="n">
-        <v/>
-      </c>
-      <c r="P203" t="n">
-        <v/>
-      </c>
       <c r="Q203" t="inlineStr">
         <is>
           <t>D0=50.01; 最新=2026-06-04; 相对D0=3.14%</t>
@@ -14529,24 +11454,6 @@
       <c r="J204" t="n">
         <v>507.45</v>
       </c>
-      <c r="K204" t="n">
-        <v/>
-      </c>
-      <c r="L204" t="n">
-        <v/>
-      </c>
-      <c r="M204" t="n">
-        <v/>
-      </c>
-      <c r="N204" t="n">
-        <v/>
-      </c>
-      <c r="O204" t="n">
-        <v/>
-      </c>
-      <c r="P204" t="n">
-        <v/>
-      </c>
       <c r="Q204" t="inlineStr">
         <is>
           <t>D0=507.57; 最新=2026-06-04; 相对D0=-0.02%</t>
@@ -14598,24 +11505,12 @@
       <c r="J205" s="4" t="n">
         <v>627.5700000000001</v>
       </c>
-      <c r="K205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O205" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P205" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K205" s="4" t="n"/>
+      <c r="L205" s="4" t="n"/>
+      <c r="M205" s="4" t="n"/>
+      <c r="N205" s="4" t="n"/>
+      <c r="O205" s="4" t="n"/>
+      <c r="P205" s="4" t="n"/>
       <c r="Q205" s="4" t="inlineStr">
         <is>
           <t>D0=622.98; 最新=2026-06-04; 相对D0=0.74%</t>
@@ -14667,24 +11562,6 @@
       <c r="J206" t="n">
         <v>80.23999999999999</v>
       </c>
-      <c r="K206" t="n">
-        <v/>
-      </c>
-      <c r="L206" t="n">
-        <v/>
-      </c>
-      <c r="M206" t="n">
-        <v/>
-      </c>
-      <c r="N206" t="n">
-        <v/>
-      </c>
-      <c r="O206" t="n">
-        <v/>
-      </c>
-      <c r="P206" t="n">
-        <v/>
-      </c>
       <c r="Q206" t="inlineStr">
         <is>
           <t>D0=80.14; 最新=2026-06-04; 相对D0=0.12%; 历史重复1次; 重复日期=2026-06-04</t>
@@ -14736,24 +11613,6 @@
       <c r="J207" t="n">
         <v>22.9</v>
       </c>
-      <c r="K207" t="n">
-        <v/>
-      </c>
-      <c r="L207" t="n">
-        <v/>
-      </c>
-      <c r="M207" t="n">
-        <v/>
-      </c>
-      <c r="N207" t="n">
-        <v/>
-      </c>
-      <c r="O207" t="n">
-        <v/>
-      </c>
-      <c r="P207" t="n">
-        <v/>
-      </c>
       <c r="Q207" t="inlineStr">
         <is>
           <t>D0=23.30; 最新=2026-06-04; 相对D0=-1.72%</t>
@@ -14805,24 +11664,6 @@
       <c r="J208" t="n">
         <v>69</v>
       </c>
-      <c r="K208" t="n">
-        <v/>
-      </c>
-      <c r="L208" t="n">
-        <v/>
-      </c>
-      <c r="M208" t="n">
-        <v/>
-      </c>
-      <c r="N208" t="n">
-        <v/>
-      </c>
-      <c r="O208" t="n">
-        <v/>
-      </c>
-      <c r="P208" t="n">
-        <v/>
-      </c>
       <c r="Q208" t="inlineStr">
         <is>
           <t>D0=68.81; 最新=2026-06-04; 相对D0=0.28%</t>
@@ -14874,24 +11715,6 @@
       <c r="J209" t="n">
         <v>30.67</v>
       </c>
-      <c r="K209" t="n">
-        <v/>
-      </c>
-      <c r="L209" t="n">
-        <v/>
-      </c>
-      <c r="M209" t="n">
-        <v/>
-      </c>
-      <c r="N209" t="n">
-        <v/>
-      </c>
-      <c r="O209" t="n">
-        <v/>
-      </c>
-      <c r="P209" t="n">
-        <v/>
-      </c>
       <c r="Q209" t="inlineStr">
         <is>
           <t>D0=30.84; 最新=2026-06-04; 相对D0=-0.55%</t>
@@ -14943,24 +11766,6 @@
       <c r="J210" t="n">
         <v>150.32</v>
       </c>
-      <c r="K210" t="n">
-        <v/>
-      </c>
-      <c r="L210" t="n">
-        <v/>
-      </c>
-      <c r="M210" t="n">
-        <v/>
-      </c>
-      <c r="N210" t="n">
-        <v/>
-      </c>
-      <c r="O210" t="n">
-        <v/>
-      </c>
-      <c r="P210" t="n">
-        <v/>
-      </c>
       <c r="Q210" t="inlineStr">
         <is>
           <t>D0=146.47; 最新=2026-06-04; 相对D0=2.63%</t>
@@ -15012,24 +11817,6 @@
       <c r="J211" t="n">
         <v>494.48</v>
       </c>
-      <c r="K211" t="n">
-        <v/>
-      </c>
-      <c r="L211" t="n">
-        <v/>
-      </c>
-      <c r="M211" t="n">
-        <v/>
-      </c>
-      <c r="N211" t="n">
-        <v/>
-      </c>
-      <c r="O211" t="n">
-        <v/>
-      </c>
-      <c r="P211" t="n">
-        <v/>
-      </c>
       <c r="Q211" t="inlineStr">
         <is>
           <t>D0=498.02; 最新=2026-06-04; 相对D0=-0.71%</t>
@@ -15081,24 +11868,12 @@
       <c r="J212" s="4" t="n">
         <v>261.31</v>
       </c>
-      <c r="K212" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L212" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M212" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N212" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O212" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P212" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K212" s="4" t="n"/>
+      <c r="L212" s="4" t="n"/>
+      <c r="M212" s="4" t="n"/>
+      <c r="N212" s="4" t="n"/>
+      <c r="O212" s="4" t="n"/>
+      <c r="P212" s="4" t="n"/>
       <c r="Q212" s="4" t="inlineStr">
         <is>
           <t>D0=267.91; 最新=2026-06-04; 相对D0=-2.46%</t>
@@ -15150,24 +11925,6 @@
       <c r="J213" t="n">
         <v>396.47</v>
       </c>
-      <c r="K213" t="n">
-        <v/>
-      </c>
-      <c r="L213" t="n">
-        <v/>
-      </c>
-      <c r="M213" t="n">
-        <v/>
-      </c>
-      <c r="N213" t="n">
-        <v/>
-      </c>
-      <c r="O213" t="n">
-        <v/>
-      </c>
-      <c r="P213" t="n">
-        <v/>
-      </c>
       <c r="Q213" t="inlineStr">
         <is>
           <t>D0=377.00; 最新=2026-06-04; 相对D0=5.16%</t>
@@ -15219,24 +11976,6 @@
       <c r="J214" t="n">
         <v>58.75</v>
       </c>
-      <c r="K214" t="n">
-        <v/>
-      </c>
-      <c r="L214" t="n">
-        <v/>
-      </c>
-      <c r="M214" t="n">
-        <v/>
-      </c>
-      <c r="N214" t="n">
-        <v/>
-      </c>
-      <c r="O214" t="n">
-        <v/>
-      </c>
-      <c r="P214" t="n">
-        <v/>
-      </c>
       <c r="Q214" t="inlineStr">
         <is>
           <t>D0=58.71; 最新=2026-06-04; 相对D0=0.07%</t>
@@ -15288,24 +12027,6 @@
       <c r="J215" t="n">
         <v>43.94</v>
       </c>
-      <c r="K215" t="n">
-        <v/>
-      </c>
-      <c r="L215" t="n">
-        <v/>
-      </c>
-      <c r="M215" t="n">
-        <v/>
-      </c>
-      <c r="N215" t="n">
-        <v/>
-      </c>
-      <c r="O215" t="n">
-        <v/>
-      </c>
-      <c r="P215" t="n">
-        <v/>
-      </c>
       <c r="Q215" t="inlineStr">
         <is>
           <t>D0=43.71; 最新=2026-06-04; 相对D0=0.53%</t>
@@ -15356,24 +12077,6 @@
       </c>
       <c r="J216" t="n">
         <v>80.23999999999999</v>
-      </c>
-      <c r="K216" t="n">
-        <v/>
-      </c>
-      <c r="L216" t="n">
-        <v/>
-      </c>
-      <c r="M216" t="n">
-        <v/>
-      </c>
-      <c r="N216" t="n">
-        <v/>
-      </c>
-      <c r="O216" t="n">
-        <v/>
-      </c>
-      <c r="P216" t="n">
-        <v/>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -15611,24 +12314,6 @@
       <c r="J228" t="n">
         <v>418.91</v>
       </c>
-      <c r="K228" t="n">
-        <v/>
-      </c>
-      <c r="L228" t="n">
-        <v/>
-      </c>
-      <c r="M228" t="n">
-        <v/>
-      </c>
-      <c r="N228" t="n">
-        <v/>
-      </c>
-      <c r="O228" t="n">
-        <v/>
-      </c>
-      <c r="P228" t="n">
-        <v/>
-      </c>
       <c r="Q228" t="inlineStr">
         <is>
           <t>D0=418.91; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出 | 预警卖出)</t>
@@ -15680,24 +12365,6 @@
       <c r="J229" t="n">
         <v>88.78</v>
       </c>
-      <c r="K229" t="n">
-        <v/>
-      </c>
-      <c r="L229" t="n">
-        <v/>
-      </c>
-      <c r="M229" t="n">
-        <v/>
-      </c>
-      <c r="N229" t="n">
-        <v/>
-      </c>
-      <c r="O229" t="n">
-        <v/>
-      </c>
-      <c r="P229" t="n">
-        <v/>
-      </c>
       <c r="Q229" t="inlineStr">
         <is>
           <t>D0=88.78; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出 | 预警卖出)</t>
@@ -15749,24 +12416,6 @@
       <c r="J230" t="n">
         <v>61.86</v>
       </c>
-      <c r="K230" t="n">
-        <v/>
-      </c>
-      <c r="L230" t="n">
-        <v/>
-      </c>
-      <c r="M230" t="n">
-        <v/>
-      </c>
-      <c r="N230" t="n">
-        <v/>
-      </c>
-      <c r="O230" t="n">
-        <v/>
-      </c>
-      <c r="P230" t="n">
-        <v/>
-      </c>
       <c r="Q230" t="inlineStr">
         <is>
           <t>D0=61.86; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出 | 预警卖出)</t>
@@ -15818,24 +12467,6 @@
       <c r="J231" t="n">
         <v>22.9</v>
       </c>
-      <c r="K231" t="n">
-        <v/>
-      </c>
-      <c r="L231" t="n">
-        <v/>
-      </c>
-      <c r="M231" t="n">
-        <v/>
-      </c>
-      <c r="N231" t="n">
-        <v/>
-      </c>
-      <c r="O231" t="n">
-        <v/>
-      </c>
-      <c r="P231" t="n">
-        <v/>
-      </c>
       <c r="Q231" t="inlineStr">
         <is>
           <t>D0=22.90; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出)</t>
@@ -15887,24 +12518,6 @@
       <c r="J232" t="n">
         <v>105.4</v>
       </c>
-      <c r="K232" t="n">
-        <v/>
-      </c>
-      <c r="L232" t="n">
-        <v/>
-      </c>
-      <c r="M232" t="n">
-        <v/>
-      </c>
-      <c r="N232" t="n">
-        <v/>
-      </c>
-      <c r="O232" t="n">
-        <v/>
-      </c>
-      <c r="P232" t="n">
-        <v/>
-      </c>
       <c r="Q232" t="inlineStr">
         <is>
           <t>D0=105.40; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出)</t>
@@ -15956,24 +12569,6 @@
       <c r="J233" t="n">
         <v>84.13</v>
       </c>
-      <c r="K233" t="n">
-        <v/>
-      </c>
-      <c r="L233" t="n">
-        <v/>
-      </c>
-      <c r="M233" t="n">
-        <v/>
-      </c>
-      <c r="N233" t="n">
-        <v/>
-      </c>
-      <c r="O233" t="n">
-        <v/>
-      </c>
-      <c r="P233" t="n">
-        <v/>
-      </c>
       <c r="Q233" t="inlineStr">
         <is>
           <t>D0=84.13; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出 | 预警卖出)</t>
@@ -16025,24 +12620,12 @@
       <c r="J234" s="4" t="n">
         <v>41.22</v>
       </c>
-      <c r="K234" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L234" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M234" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N234" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O234" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P234" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K234" s="4" t="n"/>
+      <c r="L234" s="4" t="n"/>
+      <c r="M234" s="4" t="n"/>
+      <c r="N234" s="4" t="n"/>
+      <c r="O234" s="4" t="n"/>
+      <c r="P234" s="4" t="n"/>
       <c r="Q234" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-04; 相对D0=-0.60%</t>
@@ -16063,7 +12646,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -16090,24 +12672,6 @@
       <c r="J235" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="K235" t="n">
-        <v/>
-      </c>
-      <c r="L235" t="n">
-        <v/>
-      </c>
-      <c r="M235" t="n">
-        <v/>
-      </c>
-      <c r="N235" t="n">
-        <v/>
-      </c>
-      <c r="O235" t="n">
-        <v/>
-      </c>
-      <c r="P235" t="n">
-        <v/>
-      </c>
       <c r="Q235" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-04; 相对D0=3.48%</t>
@@ -16159,24 +12723,12 @@
       <c r="J236" s="4" t="n">
         <v>188.35</v>
       </c>
-      <c r="K236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O236" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P236" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K236" s="4" t="n"/>
+      <c r="L236" s="4" t="n"/>
+      <c r="M236" s="4" t="n"/>
+      <c r="N236" s="4" t="n"/>
+      <c r="O236" s="4" t="n"/>
+      <c r="P236" s="4" t="n"/>
       <c r="Q236" s="4" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-04; 相对D0=1.97%</t>
@@ -16228,24 +12780,12 @@
       <c r="J237" s="4" t="n">
         <v>140.88</v>
       </c>
-      <c r="K237" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L237" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M237" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N237" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O237" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P237" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K237" s="4" t="n"/>
+      <c r="L237" s="4" t="n"/>
+      <c r="M237" s="4" t="n"/>
+      <c r="N237" s="4" t="n"/>
+      <c r="O237" s="4" t="n"/>
+      <c r="P237" s="4" t="n"/>
       <c r="Q237" s="4" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-04; 相对D0=3.44%</t>
@@ -16297,24 +12837,6 @@
       <c r="J238" t="n">
         <v>380.18</v>
       </c>
-      <c r="K238" t="n">
-        <v/>
-      </c>
-      <c r="L238" t="n">
-        <v/>
-      </c>
-      <c r="M238" t="n">
-        <v/>
-      </c>
-      <c r="N238" t="n">
-        <v/>
-      </c>
-      <c r="O238" t="n">
-        <v/>
-      </c>
-      <c r="P238" t="n">
-        <v/>
-      </c>
       <c r="Q238" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-04; 相对D0=23.70%</t>
@@ -16366,24 +12888,12 @@
       <c r="J239" s="4" t="n">
         <v>58.67</v>
       </c>
-      <c r="K239" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L239" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M239" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N239" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O239" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P239" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K239" s="4" t="n"/>
+      <c r="L239" s="4" t="n"/>
+      <c r="M239" s="4" t="n"/>
+      <c r="N239" s="4" t="n"/>
+      <c r="O239" s="4" t="n"/>
+      <c r="P239" s="4" t="n"/>
       <c r="Q239" s="4" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-04; 相对D0=2.11%</t>
@@ -16435,24 +12945,12 @@
       <c r="J240" s="4" t="n">
         <v>15.475</v>
       </c>
-      <c r="K240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O240" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P240" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K240" s="4" t="n"/>
+      <c r="L240" s="4" t="n"/>
+      <c r="M240" s="4" t="n"/>
+      <c r="N240" s="4" t="n"/>
+      <c r="O240" s="4" t="n"/>
+      <c r="P240" s="4" t="n"/>
       <c r="Q240" s="4" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-04; 相对D0=15.92%</t>
@@ -16504,24 +13002,12 @@
       <c r="J241" s="4" t="n">
         <v>58.75</v>
       </c>
-      <c r="K241" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L241" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M241" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N241" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O241" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P241" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K241" s="4" t="n"/>
+      <c r="L241" s="4" t="n"/>
+      <c r="M241" s="4" t="n"/>
+      <c r="N241" s="4" t="n"/>
+      <c r="O241" s="4" t="n"/>
+      <c r="P241" s="4" t="n"/>
       <c r="Q241" s="4" t="inlineStr">
         <is>
           <t>D0=57.85; 最新=2026-06-04; 相对D0=1.56%</t>
@@ -16573,24 +13059,12 @@
       <c r="J242" s="4" t="n">
         <v>58.01</v>
       </c>
-      <c r="K242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O242" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P242" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K242" s="4" t="n"/>
+      <c r="L242" s="4" t="n"/>
+      <c r="M242" s="4" t="n"/>
+      <c r="N242" s="4" t="n"/>
+      <c r="O242" s="4" t="n"/>
+      <c r="P242" s="4" t="n"/>
       <c r="Q242" s="4" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-04; 相对D0=2.67%</t>
@@ -16642,24 +13116,6 @@
       <c r="J243" t="n">
         <v>135.26</v>
       </c>
-      <c r="K243" t="n">
-        <v/>
-      </c>
-      <c r="L243" t="n">
-        <v/>
-      </c>
-      <c r="M243" t="n">
-        <v/>
-      </c>
-      <c r="N243" t="n">
-        <v/>
-      </c>
-      <c r="O243" t="n">
-        <v/>
-      </c>
-      <c r="P243" t="n">
-        <v/>
-      </c>
       <c r="Q243" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-04; 相对D0=7.00%</t>
@@ -16711,24 +13167,12 @@
       <c r="J244" s="4" t="n">
         <v>105.99</v>
       </c>
-      <c r="K244" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L244" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M244" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N244" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O244" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P244" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K244" s="4" t="n"/>
+      <c r="L244" s="4" t="n"/>
+      <c r="M244" s="4" t="n"/>
+      <c r="N244" s="4" t="n"/>
+      <c r="O244" s="4" t="n"/>
+      <c r="P244" s="4" t="n"/>
       <c r="Q244" s="4" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-04; 相对D0=-8.39%</t>
@@ -16780,24 +13224,12 @@
       <c r="J245" s="4" t="n">
         <v>264.59</v>
       </c>
-      <c r="K245" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L245" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M245" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N245" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O245" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P245" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K245" s="4" t="n"/>
+      <c r="L245" s="4" t="n"/>
+      <c r="M245" s="4" t="n"/>
+      <c r="N245" s="4" t="n"/>
+      <c r="O245" s="4" t="n"/>
+      <c r="P245" s="4" t="n"/>
       <c r="Q245" s="4" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-04; 相对D0=-7.59%</t>
@@ -16849,24 +13281,12 @@
       <c r="J246" s="4" t="n">
         <v>197.7</v>
       </c>
-      <c r="K246" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L246" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M246" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N246" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O246" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P246" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K246" s="4" t="n"/>
+      <c r="L246" s="4" t="n"/>
+      <c r="M246" s="4" t="n"/>
+      <c r="N246" s="4" t="n"/>
+      <c r="O246" s="4" t="n"/>
+      <c r="P246" s="4" t="n"/>
       <c r="Q246" s="4" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-04; 相对D0=8.05%</t>
@@ -16918,24 +13338,6 @@
       <c r="J247" t="n">
         <v>494.48</v>
       </c>
-      <c r="K247" t="n">
-        <v/>
-      </c>
-      <c r="L247" t="n">
-        <v/>
-      </c>
-      <c r="M247" t="n">
-        <v/>
-      </c>
-      <c r="N247" t="n">
-        <v/>
-      </c>
-      <c r="O247" t="n">
-        <v/>
-      </c>
-      <c r="P247" t="n">
-        <v/>
-      </c>
       <c r="Q247" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-04; 相对D0=2.88%</t>
@@ -16987,24 +13389,12 @@
       <c r="J248" s="4" t="n">
         <v>116.58</v>
       </c>
-      <c r="K248" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L248" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M248" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N248" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O248" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P248" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K248" s="4" t="n"/>
+      <c r="L248" s="4" t="n"/>
+      <c r="M248" s="4" t="n"/>
+      <c r="N248" s="4" t="n"/>
+      <c r="O248" s="4" t="n"/>
+      <c r="P248" s="4" t="n"/>
       <c r="Q248" s="4" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-04; 相对D0=26.26%</t>
@@ -17056,24 +13446,12 @@
       <c r="J249" s="4" t="n">
         <v>73.81999999999999</v>
       </c>
-      <c r="K249" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L249" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M249" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N249" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O249" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P249" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K249" s="4" t="n"/>
+      <c r="L249" s="4" t="n"/>
+      <c r="M249" s="4" t="n"/>
+      <c r="N249" s="4" t="n"/>
+      <c r="O249" s="4" t="n"/>
+      <c r="P249" s="4" t="n"/>
       <c r="Q249" s="4" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-04; 相对D0=6.12%</t>
@@ -17125,24 +13503,6 @@
       <c r="J250" t="n">
         <v>291.37</v>
       </c>
-      <c r="K250" t="n">
-        <v/>
-      </c>
-      <c r="L250" t="n">
-        <v/>
-      </c>
-      <c r="M250" t="n">
-        <v/>
-      </c>
-      <c r="N250" t="n">
-        <v/>
-      </c>
-      <c r="O250" t="n">
-        <v/>
-      </c>
-      <c r="P250" t="n">
-        <v/>
-      </c>
       <c r="Q250" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-04; 相对D0=2.24%</t>
@@ -17194,24 +13554,12 @@
       <c r="J251" s="4" t="n">
         <v>181.16</v>
       </c>
-      <c r="K251" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L251" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M251" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N251" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O251" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P251" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K251" s="4" t="n"/>
+      <c r="L251" s="4" t="n"/>
+      <c r="M251" s="4" t="n"/>
+      <c r="N251" s="4" t="n"/>
+      <c r="O251" s="4" t="n"/>
+      <c r="P251" s="4" t="n"/>
       <c r="Q251" s="4" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-04; 相对D0=5.53%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -17263,24 +13611,12 @@
       <c r="J252" s="4" t="n">
         <v>421.9</v>
       </c>
-      <c r="K252" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L252" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M252" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N252" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O252" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P252" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K252" s="4" t="n"/>
+      <c r="L252" s="4" t="n"/>
+      <c r="M252" s="4" t="n"/>
+      <c r="N252" s="4" t="n"/>
+      <c r="O252" s="4" t="n"/>
+      <c r="P252" s="4" t="n"/>
       <c r="Q252" s="4" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-04; 相对D0=16.72%</t>
@@ -17332,24 +13668,6 @@
       <c r="J253" t="n">
         <v>27.15</v>
       </c>
-      <c r="K253" t="n">
-        <v/>
-      </c>
-      <c r="L253" t="n">
-        <v/>
-      </c>
-      <c r="M253" t="n">
-        <v/>
-      </c>
-      <c r="N253" t="n">
-        <v/>
-      </c>
-      <c r="O253" t="n">
-        <v/>
-      </c>
-      <c r="P253" t="n">
-        <v/>
-      </c>
       <c r="Q253" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-04; 相对D0=43.80%</t>
@@ -17401,24 +13719,6 @@
       <c r="J254" t="n">
         <v>111.78</v>
       </c>
-      <c r="K254" t="n">
-        <v/>
-      </c>
-      <c r="L254" t="n">
-        <v/>
-      </c>
-      <c r="M254" t="n">
-        <v/>
-      </c>
-      <c r="N254" t="n">
-        <v/>
-      </c>
-      <c r="O254" t="n">
-        <v/>
-      </c>
-      <c r="P254" t="n">
-        <v/>
-      </c>
       <c r="Q254" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-04; 相对D0=-2.53%</t>
@@ -17470,24 +13770,12 @@
       <c r="J255" s="4" t="n">
         <v>133.39</v>
       </c>
-      <c r="K255" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L255" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M255" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N255" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O255" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P255" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K255" s="4" t="n"/>
+      <c r="L255" s="4" t="n"/>
+      <c r="M255" s="4" t="n"/>
+      <c r="N255" s="4" t="n"/>
+      <c r="O255" s="4" t="n"/>
+      <c r="P255" s="4" t="n"/>
       <c r="Q255" s="4" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-04; 相对D0=-0.51%</t>
@@ -17539,24 +13827,12 @@
       <c r="J256" s="4" t="n">
         <v>261.31</v>
       </c>
-      <c r="K256" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L256" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M256" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N256" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O256" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P256" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K256" s="4" t="n"/>
+      <c r="L256" s="4" t="n"/>
+      <c r="M256" s="4" t="n"/>
+      <c r="N256" s="4" t="n"/>
+      <c r="O256" s="4" t="n"/>
+      <c r="P256" s="4" t="n"/>
       <c r="Q256" s="4" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-04; 相对D0=2.38%</t>
@@ -17608,24 +13884,6 @@
       <c r="J257" t="n">
         <v>107.29</v>
       </c>
-      <c r="K257" t="n">
-        <v/>
-      </c>
-      <c r="L257" t="n">
-        <v/>
-      </c>
-      <c r="M257" t="n">
-        <v/>
-      </c>
-      <c r="N257" t="n">
-        <v/>
-      </c>
-      <c r="O257" t="n">
-        <v/>
-      </c>
-      <c r="P257" t="n">
-        <v/>
-      </c>
       <c r="Q257" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-04; 相对D0=1.55%</t>
@@ -17677,24 +13935,12 @@
       <c r="J258" s="4" t="n">
         <v>181.16</v>
       </c>
-      <c r="K258" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L258" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M258" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N258" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O258" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P258" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K258" s="4" t="n"/>
+      <c r="L258" s="4" t="n"/>
+      <c r="M258" s="4" t="n"/>
+      <c r="N258" s="4" t="n"/>
+      <c r="O258" s="4" t="n"/>
+      <c r="P258" s="4" t="n"/>
       <c r="Q258" s="4" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-04; 相对D0=11.08%</t>
@@ -17746,24 +13992,6 @@
       <c r="J259" t="n">
         <v>66.5</v>
       </c>
-      <c r="K259" t="n">
-        <v/>
-      </c>
-      <c r="L259" t="n">
-        <v/>
-      </c>
-      <c r="M259" t="n">
-        <v/>
-      </c>
-      <c r="N259" t="n">
-        <v/>
-      </c>
-      <c r="O259" t="n">
-        <v/>
-      </c>
-      <c r="P259" t="n">
-        <v/>
-      </c>
       <c r="Q259" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-04; 相对D0=2.93%</t>
@@ -17815,24 +14043,12 @@
       <c r="J260" s="4" t="n">
         <v>139.88</v>
       </c>
-      <c r="K260" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L260" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M260" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N260" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O260" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P260" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K260" s="4" t="n"/>
+      <c r="L260" s="4" t="n"/>
+      <c r="M260" s="4" t="n"/>
+      <c r="N260" s="4" t="n"/>
+      <c r="O260" s="4" t="n"/>
+      <c r="P260" s="4" t="n"/>
       <c r="Q260" s="4" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-04; 相对D0=3.06%</t>
@@ -17884,24 +14100,6 @@
       <c r="J261" t="n">
         <v>627.5700000000001</v>
       </c>
-      <c r="K261" t="n">
-        <v/>
-      </c>
-      <c r="L261" t="n">
-        <v/>
-      </c>
-      <c r="M261" t="n">
-        <v/>
-      </c>
-      <c r="N261" t="n">
-        <v/>
-      </c>
-      <c r="O261" t="n">
-        <v/>
-      </c>
-      <c r="P261" t="n">
-        <v/>
-      </c>
       <c r="Q261" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-04; 相对D0=4.51%</t>
@@ -17953,24 +14151,12 @@
       <c r="J262" s="4" t="n">
         <v>30.67</v>
       </c>
-      <c r="K262" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L262" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M262" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N262" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O262" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P262" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K262" s="4" t="n"/>
+      <c r="L262" s="4" t="n"/>
+      <c r="M262" s="4" t="n"/>
+      <c r="N262" s="4" t="n"/>
+      <c r="O262" s="4" t="n"/>
+      <c r="P262" s="4" t="n"/>
       <c r="Q262" s="4" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-04; 相对D0=23.37%</t>
@@ -18022,24 +14208,6 @@
       <c r="J263" t="n">
         <v>418.45</v>
       </c>
-      <c r="K263" t="n">
-        <v/>
-      </c>
-      <c r="L263" t="n">
-        <v/>
-      </c>
-      <c r="M263" t="n">
-        <v/>
-      </c>
-      <c r="N263" t="n">
-        <v/>
-      </c>
-      <c r="O263" t="n">
-        <v/>
-      </c>
-      <c r="P263" t="n">
-        <v/>
-      </c>
       <c r="Q263" t="inlineStr">
         <is>
           <t>D0=415.88; 最新=2026-06-04; 相对D0=0.62%</t>
@@ -18091,24 +14259,6 @@
       <c r="J264" t="n">
         <v>44.15</v>
       </c>
-      <c r="K264" t="n">
-        <v/>
-      </c>
-      <c r="L264" t="n">
-        <v/>
-      </c>
-      <c r="M264" t="n">
-        <v/>
-      </c>
-      <c r="N264" t="n">
-        <v/>
-      </c>
-      <c r="O264" t="n">
-        <v/>
-      </c>
-      <c r="P264" t="n">
-        <v/>
-      </c>
       <c r="Q264" t="inlineStr">
         <is>
           <t>D0=44.71; 最新=2026-06-04; 相对D0=-1.25%</t>
@@ -18160,24 +14310,6 @@
       <c r="J265" t="n">
         <v>16.53</v>
       </c>
-      <c r="K265" t="n">
-        <v/>
-      </c>
-      <c r="L265" t="n">
-        <v/>
-      </c>
-      <c r="M265" t="n">
-        <v/>
-      </c>
-      <c r="N265" t="n">
-        <v/>
-      </c>
-      <c r="O265" t="n">
-        <v/>
-      </c>
-      <c r="P265" t="n">
-        <v/>
-      </c>
       <c r="Q265" t="inlineStr">
         <is>
           <t>D0=16.42; 最新=2026-06-04; 相对D0=0.67%</t>
@@ -18229,24 +14361,12 @@
       <c r="J266" s="4" t="n">
         <v>217.5</v>
       </c>
-      <c r="K266" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L266" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M266" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N266" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O266" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P266" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K266" s="4" t="n"/>
+      <c r="L266" s="4" t="n"/>
+      <c r="M266" s="4" t="n"/>
+      <c r="N266" s="4" t="n"/>
+      <c r="O266" s="4" t="n"/>
+      <c r="P266" s="4" t="n"/>
       <c r="Q266" s="4" t="inlineStr">
         <is>
           <t>D0=214.60; 最新=2026-06-04; 相对D0=1.35%</t>
@@ -18298,24 +14418,6 @@
       <c r="J267" t="n">
         <v>108.03</v>
       </c>
-      <c r="K267" t="n">
-        <v/>
-      </c>
-      <c r="L267" t="n">
-        <v/>
-      </c>
-      <c r="M267" t="n">
-        <v/>
-      </c>
-      <c r="N267" t="n">
-        <v/>
-      </c>
-      <c r="O267" t="n">
-        <v/>
-      </c>
-      <c r="P267" t="n">
-        <v/>
-      </c>
       <c r="Q267" t="inlineStr">
         <is>
           <t>D0=110.93; 最新=2026-06-04; 相对D0=-2.61%</t>
@@ -18367,24 +14469,6 @@
       <c r="J268" t="n">
         <v>8.08</v>
       </c>
-      <c r="K268" t="n">
-        <v/>
-      </c>
-      <c r="L268" t="n">
-        <v/>
-      </c>
-      <c r="M268" t="n">
-        <v/>
-      </c>
-      <c r="N268" t="n">
-        <v/>
-      </c>
-      <c r="O268" t="n">
-        <v/>
-      </c>
-      <c r="P268" t="n">
-        <v/>
-      </c>
       <c r="Q268" t="inlineStr">
         <is>
           <t>D0=8.20; 最新=2026-06-04; 相对D0=-1.46%</t>
@@ -18436,24 +14520,6 @@
       <c r="J269" t="n">
         <v>88.33</v>
       </c>
-      <c r="K269" t="n">
-        <v/>
-      </c>
-      <c r="L269" t="n">
-        <v/>
-      </c>
-      <c r="M269" t="n">
-        <v/>
-      </c>
-      <c r="N269" t="n">
-        <v/>
-      </c>
-      <c r="O269" t="n">
-        <v/>
-      </c>
-      <c r="P269" t="n">
-        <v/>
-      </c>
       <c r="Q269" t="inlineStr">
         <is>
           <t>D0=82.85; 最新=2026-06-04; 相对D0=6.61%</t>
@@ -18505,24 +14571,6 @@
       <c r="J270" t="n">
         <v>428.05</v>
       </c>
-      <c r="K270" t="n">
-        <v/>
-      </c>
-      <c r="L270" t="n">
-        <v/>
-      </c>
-      <c r="M270" t="n">
-        <v/>
-      </c>
-      <c r="N270" t="n">
-        <v/>
-      </c>
-      <c r="O270" t="n">
-        <v/>
-      </c>
-      <c r="P270" t="n">
-        <v/>
-      </c>
       <c r="Q270" t="inlineStr">
         <is>
           <t>D0=427.34; 最新=2026-06-04; 相对D0=0.17%</t>
@@ -18574,24 +14622,12 @@
       <c r="J271" s="4" t="n">
         <v>26.16</v>
       </c>
-      <c r="K271" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L271" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M271" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N271" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O271" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P271" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K271" s="4" t="n"/>
+      <c r="L271" s="4" t="n"/>
+      <c r="M271" s="4" t="n"/>
+      <c r="N271" s="4" t="n"/>
+      <c r="O271" s="4" t="n"/>
+      <c r="P271" s="4" t="n"/>
       <c r="Q271" s="4" t="inlineStr">
         <is>
           <t>D0=26.37; 最新=2026-06-04; 相对D0=-0.80%</t>
@@ -18643,24 +14679,12 @@
       <c r="J272" s="4" t="n">
         <v>65.39</v>
       </c>
-      <c r="K272" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L272" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M272" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N272" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O272" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P272" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K272" s="4" t="n"/>
+      <c r="L272" s="4" t="n"/>
+      <c r="M272" s="4" t="n"/>
+      <c r="N272" s="4" t="n"/>
+      <c r="O272" s="4" t="n"/>
+      <c r="P272" s="4" t="n"/>
       <c r="Q272" s="4" t="inlineStr">
         <is>
           <t>D0=65.21; 最新=2026-06-04; 相对D0=0.28%</t>
@@ -18712,24 +14736,6 @@
       <c r="J273" t="n">
         <v>141.7</v>
       </c>
-      <c r="K273" t="n">
-        <v/>
-      </c>
-      <c r="L273" t="n">
-        <v/>
-      </c>
-      <c r="M273" t="n">
-        <v/>
-      </c>
-      <c r="N273" t="n">
-        <v/>
-      </c>
-      <c r="O273" t="n">
-        <v/>
-      </c>
-      <c r="P273" t="n">
-        <v/>
-      </c>
       <c r="Q273" t="inlineStr">
         <is>
           <t>D0=142.20; 最新=2026-06-04; 相对D0=-0.35%</t>
@@ -18781,24 +14787,6 @@
       <c r="J274" t="n">
         <v>14.82</v>
       </c>
-      <c r="K274" t="n">
-        <v/>
-      </c>
-      <c r="L274" t="n">
-        <v/>
-      </c>
-      <c r="M274" t="n">
-        <v/>
-      </c>
-      <c r="N274" t="n">
-        <v/>
-      </c>
-      <c r="O274" t="n">
-        <v/>
-      </c>
-      <c r="P274" t="n">
-        <v/>
-      </c>
       <c r="Q274" t="inlineStr">
         <is>
           <t>D0=14.85; 最新=2026-06-04; 相对D0=-0.20%</t>
@@ -18850,24 +14838,12 @@
       <c r="J275" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="K275" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L275" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M275" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N275" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O275" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P275" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K275" s="4" t="n"/>
+      <c r="L275" s="4" t="n"/>
+      <c r="M275" s="4" t="n"/>
+      <c r="N275" s="4" t="n"/>
+      <c r="O275" s="4" t="n"/>
+      <c r="P275" s="4" t="n"/>
       <c r="Q275" s="4" t="inlineStr">
         <is>
           <t>D0=12.27; 最新=2026-06-04; 相对D0=-2.20%</t>
@@ -18919,24 +14895,6 @@
       <c r="J276" t="n">
         <v>17.15</v>
       </c>
-      <c r="K276" t="n">
-        <v/>
-      </c>
-      <c r="L276" t="n">
-        <v/>
-      </c>
-      <c r="M276" t="n">
-        <v/>
-      </c>
-      <c r="N276" t="n">
-        <v/>
-      </c>
-      <c r="O276" t="n">
-        <v/>
-      </c>
-      <c r="P276" t="n">
-        <v/>
-      </c>
       <c r="Q276" t="inlineStr">
         <is>
           <t>D0=16.68; 最新=2026-06-04; 相对D0=2.82%</t>
@@ -18988,24 +14946,12 @@
       <c r="J277" s="4" t="n">
         <v>153.7</v>
       </c>
-      <c r="K277" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L277" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M277" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N277" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O277" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P277" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K277" s="4" t="n"/>
+      <c r="L277" s="4" t="n"/>
+      <c r="M277" s="4" t="n"/>
+      <c r="N277" s="4" t="n"/>
+      <c r="O277" s="4" t="n"/>
+      <c r="P277" s="4" t="n"/>
       <c r="Q277" s="4" t="inlineStr">
         <is>
           <t>D0=153.80; 最新=2026-06-04; 相对D0=-0.07%</t>
@@ -19057,24 +15003,12 @@
       <c r="J278" s="4" t="n">
         <v>378.08</v>
       </c>
-      <c r="K278" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L278" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M278" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N278" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O278" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P278" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K278" s="4" t="n"/>
+      <c r="L278" s="4" t="n"/>
+      <c r="M278" s="4" t="n"/>
+      <c r="N278" s="4" t="n"/>
+      <c r="O278" s="4" t="n"/>
+      <c r="P278" s="4" t="n"/>
       <c r="Q278" s="4" t="inlineStr">
         <is>
           <t>D0=378.08; 最新=2026-06-04; 相对D0=0.00%</t>
@@ -19171,7 +15105,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19183,7 +15116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -19302,7 +15235,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="11" t="n">
@@ -19564,7 +15497,6 @@
       <c r="F8" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>68.5</v>
       </c>
@@ -19716,7 +15648,6 @@
       <c r="F11" t="n">
         <v>14.7</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>14.68</v>
       </c>
@@ -19735,7 +15666,6 @@
       <c r="M11" s="20" t="n">
         <v>0.002041</v>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -19868,7 +15798,6 @@
       <c r="F14" t="n">
         <v>15.58</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>15.25</v>
       </c>
@@ -19887,7 +15816,6 @@
       <c r="M14" s="21" t="n">
         <v>-0.048781</v>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -20043,7 +15971,6 @@
       <c r="M17" s="20" t="n">
         <v>0.001639</v>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -20652,9 +16579,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>17 商业航天</t>
@@ -20700,9 +16625,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -20752,9 +16675,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -20800,9 +16721,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="15" t="n"/>
       <c r="C39" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -20848,9 +16767,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="15" t="n"/>
       <c r="C40" s="4" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -20896,9 +16813,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -20944,9 +16859,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -21076,7 +16989,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21088,7 +17000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21389,7 +17301,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="11" t="n">
@@ -21714,7 +17626,6 @@
       <c r="O11" s="21" t="n">
         <v>-0.013695</v>
       </c>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -21917,7 +17828,6 @@
       <c r="F15" t="n">
         <v>1921.71</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1940.04</v>
       </c>
@@ -21942,7 +17852,6 @@
       <c r="O15" s="20" t="n">
         <v>0.10896</v>
       </c>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16"/>
     <row r="17">
@@ -22205,9 +18114,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="15" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -22259,9 +18166,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="15" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -22313,9 +18218,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="15" t="n"/>
       <c r="C29" s="4" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -22367,9 +18270,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="15" t="n"/>
       <c r="C30" s="4" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -22425,9 +18326,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="15" t="n"/>
       <c r="C31" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -22479,9 +18378,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="15" t="n"/>
       <c r="C32" s="4" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -22533,9 +18430,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="15" t="n"/>
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -22587,9 +18482,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="15" t="n"/>
       <c r="C34" s="4" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -22641,9 +18534,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -22779,7 +18670,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22791,7 +18681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -23543,7 +19433,6 @@
       <c r="Q12" s="20" t="n">
         <v>0.041136</v>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23572,7 +19461,6 @@
       <c r="F13" t="n">
         <v>290.01</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>285</v>
       </c>
@@ -23671,7 +19559,6 @@
       <c r="Q14" s="20" t="n">
         <v>0.029641</v>
       </c>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23700,7 +19587,6 @@
       <c r="F15" t="n">
         <v>67.38</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>66.94</v>
       </c>
@@ -23764,7 +19650,6 @@
       <c r="F16" t="n">
         <v>1069.4399</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1068.04</v>
       </c>
@@ -23795,7 +19680,6 @@
       <c r="Q16" s="20" t="n">
         <v>0.01843</v>
       </c>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -24496,9 +20380,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -24556,9 +20438,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -24616,9 +20496,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -24676,9 +20554,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -24794,9 +20670,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24808,7 +20681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -25103,7 +20976,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
@@ -25169,7 +21042,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="11" t="n">
@@ -25385,7 +21258,6 @@
       <c r="F9" t="n">
         <v>190.96</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>203.7</v>
       </c>
@@ -25422,7 +21294,6 @@
       <c r="S9" s="20" t="n">
         <v>0.237641</v>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25451,7 +21322,6 @@
       <c r="F10" t="n">
         <v>90.87</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>91.09</v>
       </c>
@@ -25632,7 +21502,6 @@
       <c r="S12" s="20" t="n">
         <v>0.029488</v>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -26051,9 +21920,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="15" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -26117,9 +21984,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="15" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -26228,10 +22093,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26243,7 +22104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -26714,7 +22575,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
@@ -26872,7 +22733,6 @@
       <c r="F9" t="n">
         <v>105.89</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>104.27</v>
       </c>
@@ -28146,7 +24006,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -28199,7 +24059,6 @@
       <c r="U26" s="20" t="n">
         <v>0.012378</v>
       </c>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -28222,7 +24081,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -28366,7 +24225,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
@@ -28712,9 +24571,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" s="4" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -28784,9 +24641,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -28856,9 +24711,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="15" t="n"/>
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -28928,9 +24781,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="15" t="n"/>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -29000,9 +24851,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="15" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -29072,9 +24921,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="15" t="n"/>
       <c r="C46" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -29144,9 +24991,7 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="15" t="n"/>
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -29287,8 +25132,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29300,7 +25143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -29461,24 +25304,12 @@
       <c r="J3" s="4" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29530,24 +25361,12 @@
       <c r="J4" s="4" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29599,24 +25418,12 @@
       <c r="J5" s="4" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29668,24 +25475,12 @@
       <c r="J6" s="4" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29737,24 +25532,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29806,24 +25583,12 @@
       <c r="J8" s="4" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29875,24 +25640,12 @@
       <c r="J9" s="4" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29944,24 +25697,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30013,24 +25748,12 @@
       <c r="J11" s="4" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30082,24 +25805,12 @@
       <c r="J12" s="4" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30151,24 +25862,12 @@
       <c r="J13" s="4" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30220,24 +25919,12 @@
       <c r="J14" s="4" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30289,24 +25976,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30358,24 +26027,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30427,24 +26078,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30496,24 +26129,12 @@
       <c r="J18" s="4" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30565,24 +26186,12 @@
       <c r="J19" s="4" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30634,24 +26243,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30703,24 +26294,12 @@
       <c r="J21" s="4" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30957,24 +26536,12 @@
       <c r="J33" s="4" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="4" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -31019,11 +26586,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31035,7 +26597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X54"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -31220,7 +26782,6 @@
       <c r="F3" t="n">
         <v>22.51</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
@@ -31712,7 +27273,6 @@
       <c r="F9" t="n">
         <v>181.49</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>177.62</v>
       </c>
@@ -32204,7 +27764,6 @@
       <c r="F15" t="n">
         <v>16.12</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>15.47</v>
       </c>
@@ -32368,7 +27927,6 @@
       <c r="F17" t="n">
         <v>610.26</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>612.34</v>
       </c>
@@ -32774,7 +28332,6 @@
       <c r="F22" t="n">
         <v>141.22</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>136.2</v>
       </c>
@@ -32856,7 +28413,6 @@
       <c r="F23" t="n">
         <v>58.81</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>57.46</v>
       </c>
@@ -32938,7 +28494,6 @@
       <c r="F24" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>84.64</v>
       </c>
@@ -33014,7 +28569,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
@@ -33102,7 +28657,6 @@
       <c r="F26" t="n">
         <v>426.01</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>433.59</v>
       </c>
@@ -33151,7 +28705,6 @@
       <c r="W26" s="21" t="n">
         <v>-0.017746</v>
       </c>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -33174,7 +28727,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -33502,7 +29055,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
@@ -33584,7 +29137,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
@@ -34020,9 +29573,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="15" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -34130,11 +29681,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -34442,7 +29988,6 @@
       <c r="V3" t="n">
         <v>79.5</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.09; 4H分金=50.79</t>
@@ -34530,7 +30075,6 @@
       <c r="V4" t="n">
         <v>177.4799957275391</v>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.15; 4H分金=46.77</t>
@@ -34656,7 +30200,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -34888,7 +30432,6 @@
       <c r="V8" t="n">
         <v>495</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-03; 1出价格=495.00; Gann0=405.86; 段涨幅=21.96%</t>
@@ -34976,7 +30519,6 @@
       <c r="V9" t="n">
         <v>495</v>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=41.55; 4H分金=27.51</t>
@@ -35244,7 +30786,6 @@
       <c r="V12" t="n">
         <v>93.69999694824219</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=93.70; Gann0=80.98; 段涨幅=15.71%</t>
@@ -35332,7 +30873,6 @@
       <c r="V13" t="n">
         <v>93.69999694824219</v>
       </c>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.13; 4H分金=40.89</t>
@@ -35414,8 +30954,6 @@
       <c r="T14" t="b">
         <v>0</v>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="n">
         <v>91</v>
       </c>
@@ -35506,7 +31044,6 @@
       <c r="V15" t="n">
         <v>122.3000030517578</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.26; 4H分金=49.84</t>
@@ -35774,7 +31311,6 @@
       <c r="V18" t="n">
         <v>94.39499664306641</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=65.76; 4H分金=53.91</t>
@@ -35862,7 +31398,6 @@
       <c r="V19" t="n">
         <v>474.0299987792969</v>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.06; 4H分金=51.09</t>
@@ -36220,7 +31755,6 @@
       <c r="V23" t="n">
         <v>785.6599731445312</v>
       </c>
-      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.58; 4H分金=46.09</t>
@@ -36488,7 +32022,6 @@
       <c r="V26" t="n">
         <v>147.3800048828125</v>
       </c>
-      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=52.00; 4H分金=50.23</t>
@@ -36570,8 +32103,6 @@
       <c r="T27" t="b">
         <v>0</v>
       </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
         <v>88</v>
       </c>
@@ -36656,8 +32187,6 @@
       <c r="T28" t="b">
         <v>0</v>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="n">
         <v>81</v>
       </c>
@@ -37018,7 +32547,6 @@
       <c r="V32" t="n">
         <v>332.4599914550781</v>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=64.77; 4H分金=52.65</t>
@@ -37376,7 +32904,6 @@
       <c r="V36" t="n">
         <v>70.70700073242188</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-03; 1出价格=70.71; Gann0=46.00; 段涨幅=53.71%</t>
@@ -37464,7 +32991,6 @@
       <c r="V37" t="n">
         <v>70.70700073242188</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.63; 4H分金=37.70</t>
@@ -37732,7 +33258,6 @@
       <c r="V40" t="n">
         <v>1049.530029296875</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=52.02; 4H分金=52.67</t>
@@ -37820,7 +33345,6 @@
       <c r="V41" t="n">
         <v>13.64999961853027</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.98; 4H分金=50.09</t>
@@ -37998,7 +33522,6 @@
       <c r="V43" t="n">
         <v>24.5</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-29; 1出价格=24.50; Gann0=20.89; 段涨幅=17.28%</t>
@@ -38086,7 +33609,6 @@
       <c r="V44" t="n">
         <v>1089.2900390625</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=63.38; 4H分金=46.91</t>
@@ -38444,7 +33966,6 @@
       <c r="V48" t="n">
         <v>60.5</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.82; 4H分金=49.21</t>
@@ -38622,7 +34143,6 @@
       <c r="V50" t="n">
         <v>112.2099990844727</v>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=112.21; Gann0=103.14; 段涨幅=8.79%</t>
@@ -38794,8 +34314,6 @@
       <c r="T52" t="b">
         <v>0</v>
       </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="n">
         <v>94</v>
       </c>
@@ -38976,7 +34494,6 @@
       <c r="V54" t="n">
         <v>89.72000122070312</v>
       </c>
-      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-03; 1出价格=89.72; Gann0=78.50; 段涨幅=14.29%</t>
@@ -39064,7 +34581,6 @@
       <c r="V55" t="n">
         <v>89.72000122070312</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.65; 4H分金=38.40</t>
@@ -39422,7 +34938,6 @@
       <c r="V59" t="n">
         <v>345.1799926757812</v>
       </c>
-      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.34; 4H分金=45.37</t>
@@ -39815,7 +35330,6 @@
       <c r="D3" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46168</v>
       </c>
@@ -39864,7 +35378,6 @@
           <t>18 化肥</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -40027,7 +35540,6 @@
       <c r="D7" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="8" t="n">
         <v>46175</v>
       </c>
@@ -40187,7 +35699,6 @@
       <c r="D10" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="8" t="n">
         <v>46174</v>
       </c>
@@ -40347,7 +35858,6 @@
       <c r="D13" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="8" t="n">
         <v>46164</v>
       </c>
@@ -40399,7 +35909,6 @@
       <c r="D14" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="8" t="n">
         <v>46168</v>
       </c>
@@ -40451,7 +35960,6 @@
       <c r="D15" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="8" t="n">
         <v>46174</v>
       </c>
@@ -40503,7 +36011,6 @@
       <c r="D16" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="8" t="n">
         <v>46175</v>
       </c>
@@ -40609,7 +36116,6 @@
       <c r="D18" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="8" t="n">
         <v>46174</v>
       </c>
@@ -40661,7 +36167,6 @@
       <c r="D19" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="8" t="n">
         <v>46168</v>
       </c>
@@ -40767,7 +36272,6 @@
       <c r="D21" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="8" t="n">
         <v>46164</v>
       </c>
@@ -40819,7 +36323,6 @@
       <c r="D22" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="8" t="n">
         <v>46175</v>
       </c>
@@ -40868,7 +36371,6 @@
           <t>19 COWOS</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" s="8" t="n">
         <v>46164</v>
       </c>
@@ -40977,7 +36479,6 @@
       <c r="D25" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="8" t="n">
         <v>46164</v>
       </c>
@@ -41137,7 +36638,6 @@
       <c r="D28" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" s="8" t="n">
         <v>46164</v>
       </c>
@@ -41457,7 +36957,6 @@
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" s="8" t="n">
         <v>46177</v>
       </c>
@@ -42139,7 +37638,6 @@
       <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" s="8" t="n">
         <v>46175</v>
       </c>
@@ -42821,7 +38319,6 @@
       <c r="I28" t="n">
         <v>5</v>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" s="8" t="n">
         <v>46171</v>
       </c>
@@ -42933,7 +38430,6 @@
       <c r="I30" t="n">
         <v>7</v>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" s="8" t="n">
         <v>46169</v>
       </c>
@@ -42965,7 +38461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -43161,7 +38657,6 @@
           <t>2026-05-22 (90), 2026-05-27 (100)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -43218,7 +38713,7 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F8" s="11" t="n">
@@ -43569,7 +39064,6 @@
           <t>2026-05-26 (87), 2026-05-28 (87)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -43701,7 +39195,6 @@
           <t>2026-06-01 (97)</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -43735,7 +39228,6 @@
           <t>2026-06-02 (70)</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -43764,8 +39256,6 @@
       <c r="F24" t="n">
         <v>301.77</v>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -43897,7 +39387,6 @@
           <t>2026-05-28 (70)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -43931,7 +39420,6 @@
           <t>2026-05-28 (70)</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -43960,8 +39448,6 @@
       <c r="F30" t="n">
         <v>52.07</v>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31"/>
     <row r="32">
@@ -44162,9 +39648,7 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -44192,9 +39676,7 @@
           <t>BHP</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="15" t="n"/>
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -44222,9 +39704,7 @@
           <t>IREN</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="15" t="n"/>
       <c r="C44" s="4" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -44252,9 +39732,7 @@
           <t>MOS</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="15" t="n"/>
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>18 农业/化肥</t>
@@ -44282,9 +39760,7 @@
           <t>RIO</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="15" t="n"/>
       <c r="C46" s="4" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -44312,9 +39788,7 @@
           <t>SOLS</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="15" t="n"/>
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t>23 杂项</t>
@@ -44342,9 +39816,7 @@
           <t>TLN</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B48" s="16" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -44363,8 +39835,6 @@
       <c r="F48" t="n">
         <v>378.08</v>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49"/>
     <row r="50">
@@ -44456,7 +39926,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44468,7 +39937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -44885,14 +40354,12 @@
       <c r="F11" t="n">
         <v>43.71</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>43.94</v>
       </c>
       <c r="I11" s="20" t="n">
         <v>0.005262</v>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -44961,14 +40428,12 @@
       <c r="F13" t="n">
         <v>282.27</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>282.85</v>
       </c>
       <c r="I13" s="20" t="n">
         <v>0.002055</v>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -45088,7 +40553,6 @@
       <c r="I16" s="20" t="n">
         <v>0.102244</v>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -45128,7 +40592,6 @@
       <c r="I17" s="21" t="n">
         <v>-0.007108</v>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -45204,7 +40667,6 @@
       <c r="I19" s="20" t="n">
         <v>0.026285</v>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45244,7 +40706,6 @@
       <c r="I20" s="21" t="n">
         <v>-0.024635</v>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -45267,7 +40728,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
@@ -45364,7 +40825,6 @@
       <c r="I23" s="21" t="n">
         <v>-0.005512</v>
       </c>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24"/>
     <row r="25">
@@ -45586,9 +41046,7 @@
           <t>APLD</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="4" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -45622,9 +41080,7 @@
           <t>CPNG</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="4" t="inlineStr">
         <is>
           <t>23 杂项</t>
@@ -45658,9 +41114,7 @@
           <t>CRDO</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="4" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -45694,9 +41148,7 @@
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="4" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -45730,9 +41182,7 @@
           <t>EOSE</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="16" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -45751,14 +41201,12 @@
       <c r="F39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>8.08</v>
       </c>
       <c r="I39" s="21" t="n">
         <v>-0.014634</v>
       </c>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -45766,9 +41214,7 @@
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="15" t="n"/>
       <c r="C40" s="4" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -45802,9 +41248,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="16" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -45823,14 +41267,12 @@
       <c r="F41" t="n">
         <v>427.34</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>428.05</v>
       </c>
       <c r="I41" s="20" t="n">
         <v>0.001661</v>
       </c>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -45838,9 +41280,7 @@
           <t>NNE</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -45874,9 +41314,7 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="15" t="n"/>
       <c r="C43" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -45910,9 +41348,7 @@
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="16" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -45931,14 +41367,12 @@
       <c r="F44" t="n">
         <v>142.2</v>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>141.7</v>
       </c>
       <c r="I44" s="21" t="n">
         <v>-0.003516</v>
       </c>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -45946,9 +41380,7 @@
           <t>RUN</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="16" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>10 太阳能</t>
@@ -45967,14 +41399,12 @@
       <c r="F45" t="n">
         <v>14.85</v>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>14.82</v>
       </c>
       <c r="I45" s="21" t="n">
         <v>-0.00202</v>
       </c>
-      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -45982,9 +41412,7 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="15" t="n"/>
       <c r="C46" s="4" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -46018,9 +41446,7 @@
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="15" t="n"/>
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -46054,9 +41480,7 @@
           <t>VST</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B48" s="16" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -46075,14 +41499,12 @@
       <c r="F48" t="n">
         <v>153.8</v>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>153.7</v>
       </c>
       <c r="I48" s="21" t="n">
         <v>-0.00065</v>
       </c>
-      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49"/>
     <row r="50">
@@ -46174,7 +41596,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46454,7 +41875,6 @@
       <c r="K6" s="21" t="n">
         <v>-0.017167</v>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -46569,7 +41989,7 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F9" s="11" t="n">
@@ -46615,7 +42035,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F10" s="11" t="n">
@@ -46661,7 +42081,7 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F11" s="11" t="n">
@@ -47630,7 +43050,6 @@
       <c r="K32" s="20" t="n">
         <v>0.001941</v>
       </c>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -47768,7 +43187,6 @@
       <c r="K35" s="20" t="n">
         <v>0.012656</v>
       </c>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -47814,7 +43232,6 @@
       <c r="K36" s="21" t="n">
         <v>-0.037304</v>
       </c>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -47931,7 +43348,6 @@
       <c r="F39" t="n">
         <v>315.2</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>310.26</v>
       </c>
@@ -47977,7 +43393,6 @@
       <c r="F40" t="n">
         <v>72.33</v>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>69.02</v>
       </c>
@@ -47990,7 +43405,6 @@
       <c r="K40" s="21" t="n">
         <v>-0.054473</v>
       </c>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -48019,7 +43433,6 @@
       <c r="F41" t="n">
         <v>11.72</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>11.1</v>
       </c>
